--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>280139</t>
+          <t>181872</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>79379</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>MONICA ISABEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARMIENTO </t>
+          <t>PÉREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MATÍAS</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,28 +740,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9933758496</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>8123577788</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MALAGA 3141</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15-09-1988</t>
+          <t>05-10-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SESM99612@GMAIL.COM</t>
+          <t>MONICAISABELPEREZROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2025 04:41:08</t>
+          <t>04-07-2023 19:04:36</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -771,36 +775,44 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>18-02-2026 07:06:00</t>
+          <t>23-02-2026 18:12:17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:11:17</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,14 +820,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180522455900005062</t>
+          <t>26180522594580005639</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -832,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>284451</t>
+          <t>280139</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>81952</t>
+          <t>77640</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANGEL GAEL</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t xml:space="preserve">SARMIENTO </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>MATÍAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,7 +879,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8123362386</t>
+          <t>9933758496</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -878,17 +890,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-10-2007</t>
+          <t>15-09-1988</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ZGAL4625@GMAIL.COM</t>
+          <t>SESM99612@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>24-03-2025 04:21:12</t>
+          <t>24-02-2025 04:41:08</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -903,28 +915,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 11:35:50</t>
+          <t>18-02-2026 07:06:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -935,40 +947,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26180522007340003083</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522455900005062</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>332998</t>
+          <t>284451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUIS MIGUEL</t>
+          <t>ANGEL GAEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -998,14 +1006,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8112721434</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>GUADIANA 205</t>
-        </is>
-      </c>
+          <t>8123362386</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1013,64 +1017,56 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>04-08-1990</t>
+          <t>27-10-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LUISMIGUEL@GMAIL.COM</t>
+          <t>ZGAL4625@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>07-01-2026 19:52:40</t>
+          <t>24-03-2025 04:21:12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20-02-2026 19:53:19</t>
+          <t>02-02-2026 11:35:50</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>20-02-2026 19:52:31</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1078,36 +1074,40 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522536370005424</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26180522007340003083</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>239891</t>
+          <t>332998</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1117,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR AZAEL </t>
+          <t>LUIS MIGUEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABURTO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,10 +1137,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8189633349</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>8112721434</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GUADIANA 205</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1148,56 +1152,64 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>09-06-2009</t>
+          <t>04-08-1990</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CADA090909CESAR@GMAIL.COM</t>
+          <t>LUISMIGUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>14-06-2024 19:41:16</t>
+          <t>07-01-2026 19:52:40</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-02-2026 14:21:46</t>
+          <t>20-02-2026 19:53:19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20-02-2026 19:52:31</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1205,14 +1217,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522075620003383</t>
+          <t>26180522536370005424</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1229,12 +1241,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>339866</t>
+          <t>239891</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1244,17 +1256,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KEVIN</t>
+          <t xml:space="preserve">CESAR AZAEL </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ABURTO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1264,7 +1276,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8117557918</t>
+          <t>8189633349</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,17 +1287,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>09-06-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LOGISTICAEMANUEL_NORESTE@TRANSPORTESLUKE.COM</t>
+          <t>CADA090909CESAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 06:32:23</t>
+          <t>14-06-2024 19:41:16</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1310,18 +1322,18 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 06:39:17</t>
+          <t>04-02-2026 14:21:46</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1332,7 +1344,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26180521998770003046</t>
+          <t>26180522075620003383</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1344,24 +1356,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>318392</t>
+          <t>339866</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,17 +1383,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDGAR ALEJANDRO </t>
+          <t>KEVIN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BERNAL </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1391,14 +1403,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8131546744</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CIRCUITO DE LOS ERUDITOS 1120</t>
-        </is>
-      </c>
+          <t>8117557918</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1406,38 +1414,42 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27-10-1992</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>EDGARCANTU.B@HOTMAIL.COM</t>
+          <t>LOGISTICAEMANUEL_NORESTE@TRANSPORTESLUKE.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>13-10-2025 08:26:51</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>02-02-2026 06:32:23</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-02-2026 10:14:11</t>
+          <t>02-02-2026 06:39:17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1445,21 +1457,13 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-02-2026 10:13:38</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1467,27 +1471,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26180522004370003069</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>LILIANA SARAHI MORALES VARGAS</t>
-        </is>
-      </c>
+          <t>26180521998770003046</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1499,12 +1495,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340362</t>
+          <t>298061</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>95559</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,17 +1510,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>DAVID OZIEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>RINCON</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">BERLANGA </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1534,14 +1530,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8116965605</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>EL PERAL 201</t>
-        </is>
-      </c>
+          <t>8113134704</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1549,60 +1541,56 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-04-1989</t>
+          <t>06-08-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MARVALAPER@GMAIL.COM</t>
+          <t>DAVIDOZIELRINCONB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 19:10:17</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>12-06-2025 15:05:36</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 19:14:26</t>
+          <t>18-02-2026 17:16:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-02-2026 19:13:51</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1610,19 +1598,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522021870003146</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26180522468690005145</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1634,12 +1626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>298061</t>
+          <t>336107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>95559</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1649,17 +1641,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DAVID OZIEL</t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RINCON</t>
+          <t>LOMELI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERLANGA </t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1669,7 +1661,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8113134704</t>
+          <t>8119654617</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1680,17 +1672,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>06-08-2010</t>
+          <t>25-01-2012</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DAVIDOZIELRINCONB@GMAIL.COM</t>
+          <t>SEBASTI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>12-06-2025 15:05:36</t>
+          <t>19-01-2026 18:01:39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1715,18 +1707,18 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18-02-2026 17:16:52</t>
+          <t>04-02-2026 17:51:43</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1737,15 +1729,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26180522468690005145</t>
+          <t>26180522083650003457</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1753,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1765,12 +1761,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>336107</t>
+          <t>340362</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1780,17 +1776,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LOMELI</t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1800,10 +1796,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8119654617</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>8116965605</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EL PERAL 201</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1811,56 +1811,60 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25-01-2012</t>
+          <t>18-04-1989</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SEBASTI@GMAIL.COM</t>
+          <t>MARVALAPER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>19-01-2026 18:01:39</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 19:10:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:51:43</t>
+          <t>02-02-2026 19:14:26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-02-2026 19:13:51</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1868,22 +1872,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26180522083650003457</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522021870003146</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2166,12 +2162,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339825</t>
+          <t>205336</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2181,17 +2177,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PEDRO ALFREDO</t>
+          <t>DYLAN ALEXANDER</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VILLARRUEL</t>
+          <t>BALDERAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2201,14 +2197,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5534742862</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AV. BOSQUES DE LA HUASTECA 301</t>
-        </is>
-      </c>
+          <t>8121541310</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2216,64 +2208,52 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>09-02-1996</t>
+          <t>22-05-2007</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PEDVILLARRUEL@GMAIL.COM</t>
+          <t>BALDAAS8308@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>01-02-2026 13:54:36</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-11-2023 17:09:47</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>01-02-2026 13:58:26</t>
+          <t>23-02-2026 18:01:28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>01-02-2026 13:57:54</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2281,36 +2261,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26180521991760003025</t>
+          <t>26180522593460005633</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340436</t>
+          <t>339825</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,17 +2300,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CESAR ALBERTO</t>
+          <t>PEDRO ALFREDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VILLARRUEL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2340,12 +2320,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8119064102</t>
+          <t>5534742862</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CALLE 9 PONIENTE 401</t>
+          <t>AV. BOSQUES DE LA HUASTECA 301</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2355,48 +2335,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11-03-1995</t>
+          <t>09-02-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CESARRODRIGUEZSOLIS@HOTMAIL.COM</t>
+          <t>PEDVILLARRUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 06:45:44</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>01-02-2026 13:54:36</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-02-2026 17:36:18</t>
+          <t>01-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>06-02-2026 17:35:48</t>
+          <t>01-02-2026 13:57:54</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2406,7 +2390,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2416,27 +2400,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26180522143130003746</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180521991760003025</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2448,12 +2424,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340566</t>
+          <t>340436</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2463,17 +2439,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HUMBERTO JOSE</t>
+          <t>CESAR ALBERTO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MONCADA</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2483,10 +2459,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8135551657</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>8119064102</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CALLE 9 PONIENTE 401</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2494,56 +2474,60 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-07-2007</t>
+          <t>11-03-1995</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>HUMBERTOGOMEZMONCADA@GAMIL.COM</t>
+          <t>CESARRODRIGUEZSOLIS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-02-2026 13:28:20</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 06:45:44</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-02-2026 13:29:46</t>
+          <t>06-02-2026 17:36:18</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>06-02-2026 17:35:48</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2551,14 +2535,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26180522039700003220</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26180522143130003746</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2575,12 +2567,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341015</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2590,17 +2582,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RAUL EDUARDO</t>
+          <t>HUMBERTO JOSE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECHAVARRIA </t>
+          <t>MONCADA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2610,14 +2602,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8134126486</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>VALLADOLID 3136</t>
-        </is>
-      </c>
+          <t>8135551657</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2625,60 +2613,56 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25-04-1996</t>
+          <t>28-07-2007</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EDUARDORAUL@GMAIL.COM</t>
+          <t>HUMBERTOGOMEZMONCADA@GAMIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 14:33:15</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>03-02-2026 13:28:20</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 14:36:49</t>
+          <t>03-02-2026 13:29:46</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>04-02-2026 14:36:26</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2686,36 +2670,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522076060003386</t>
+          <t>26180522039700003220</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341078</t>
+          <t>341253</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2725,17 +2709,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>RUBI YAZMIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CID</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2745,32 +2729,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8180764767</t>
+          <t>6141527994</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CAÑON DE LA MIELERA 213</t>
+          <t>ASTORGA 322</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>14-11-1996</t>
+          <t>05-09-1987</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>XAVIERCID21@GMAIL.COM</t>
+          <t>MONTOYARUBI050987@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 16:35:12</t>
+          <t>05-02-2026 09:33:42</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2791,17 +2775,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 16:43:33</t>
+          <t>06-02-2026 09:23:42</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-02-2026 16:40:54</t>
+          <t>06-02-2026 09:22:38</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2821,10 +2805,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26180522080330003428</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26180522132530003676</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2833,7 +2821,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2845,12 +2833,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340721</t>
+          <t>341015</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2860,17 +2848,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DANIEL SANTIAGO</t>
+          <t>RAUL EDUARDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t xml:space="preserve">ECHAVARRIA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2880,10 +2868,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8112644616</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>8134126486</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>VALLADOLID 3136</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2891,56 +2883,60 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20-05-2004</t>
+          <t>25-04-1996</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>DANI_VV07@OUTLOOK.ES</t>
+          <t>EDUARDORAUL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-02-2026 17:18:04</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 14:33:15</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:43:55</t>
+          <t>04-02-2026 14:36:49</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>04-02-2026 14:36:26</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2948,36 +2944,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26180522083200003455</t>
+          <t>26180522076060003386</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>316119</t>
+          <t>341078</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2987,17 +2983,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WILLIAM</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CID</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CADENA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3007,12 +3003,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8125770715</t>
+          <t>8180764767</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PAMPLONA</t>
+          <t>CAÑON DE LA MIELERA 213</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3022,17 +3018,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>03-11-2008</t>
+          <t>14-11-1996</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>WILLIAM.RODRIGUEZ@UNIAM.EDU.MX</t>
+          <t>XAVIERCID21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28-09-2025 19:31:41</t>
+          <t>04-02-2026 16:35:12</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3053,17 +3049,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 15:08:37</t>
+          <t>04-02-2026 16:43:33</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 15:07:57</t>
+          <t>04-02-2026 16:40:54</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3083,14 +3079,10 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26180522013870003124</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522080330003428</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3111,12 +3103,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>318215</t>
+          <t>340721</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>18539</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3126,17 +3118,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PERLA JAZMIN</t>
+          <t>DANIEL SANTIAGO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>VALDES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3146,75 +3138,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8119127750</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SANTA CATARINA</t>
-        </is>
-      </c>
+          <t>8112644616</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-05-1989</t>
+          <t>20-05-2004</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JAZZGALVAE@GMAIL.COM</t>
+          <t>DANI_VV07@OUTLOOK.ES</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>11-10-2025 07:14:32</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>03-02-2026 17:18:04</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:44</t>
+          <t>04-02-2026 17:43:55</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:01:13</t>
-        </is>
-      </c>
+          <t>04-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3222,23 +3206,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26180522205010003980</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522083200003455</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3250,12 +3230,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341151</t>
+          <t>340753</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3265,17 +3245,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OLGA JAZMIN</t>
+          <t>PAOLA RUBI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PERALES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3285,14 +3265,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8113832951</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CALLE 9 PONIENTE 401</t>
-        </is>
-      </c>
+          <t>8136096465</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3300,60 +3276,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>04-01-1995</t>
+          <t>23-11-2009</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>OJPERALESRIVERA@HOTMAIL.COM</t>
+          <t>PAOLARUBILOPEZ92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-02-2026 18:42:56</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>03-02-2026 17:53:20</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>06-02-2026 17:33:50</t>
+          <t>03-02-2026 17:54:41</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>06-02-2026 17:33:09</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3361,44 +3333,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26180522143050003744</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522051200003314</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340753</t>
+          <t>341151</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,17 +3372,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PAOLA RUBI</t>
+          <t>OLGA JAZMIN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PERALES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3428,10 +3392,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8136096465</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>8113832951</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CALLE 9 PONIENTE 401</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3439,56 +3407,60 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-11-2009</t>
+          <t>04-01-1995</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PAOLARUBILOPEZ92@GMAIL.COM</t>
+          <t>OJPERALESRIVERA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-02-2026 17:53:20</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 18:42:56</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-02-2026 17:54:41</t>
+          <t>06-02-2026 17:33:50</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>06-02-2026 17:33:09</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3496,36 +3468,44 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26180522051200003314</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26180522143050003744</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341253</t>
+          <t>316119</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3535,17 +3515,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RUBI YAZMIN</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3555,32 +3535,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6141527994</t>
+          <t>8125770715</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ASTORGA 322</t>
+          <t>PAMPLONA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>05-09-1987</t>
+          <t>03-11-2008</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MONTOYARUBI050987@GMAIL.COM</t>
+          <t>WILLIAM.RODRIGUEZ@UNIAM.EDU.MX</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-02-2026 09:33:42</t>
+          <t>28-09-2025 19:31:41</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3601,17 +3581,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-02-2026 09:23:42</t>
+          <t>02-02-2026 15:08:37</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>06-02-2026 09:22:38</t>
+          <t>02-02-2026 15:07:57</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3631,7 +3611,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26180522132530003676</t>
+          <t>26180522013870003124</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3647,7 +3627,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3659,12 +3639,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>339753</t>
+          <t>318215</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3674,17 +3654,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FEDERICO</t>
+          <t>PERLA JAZMIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AMARO</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3694,32 +3674,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8131096958</t>
+          <t>8119127750</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 DE MAYO 187</t>
+          <t>SANTA CATARINA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22-05-1994</t>
+          <t>10-05-1989</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>AMARODAVILA377@GMAIL.COM</t>
+          <t>JAZZGALVAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>01-02-2026 09:47:57</t>
+          <t>11-10-2025 07:14:32</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3730,7 +3710,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3740,17 +3720,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>01-02-2026 09:54:01</t>
+          <t>09-02-2026 18:01:44</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:56</t>
+          <t>09-02-2026 18:01:13</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3770,10 +3750,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26180521988280003004</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+          <t>26180522205010003980</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3782,7 +3766,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3794,12 +3778,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>245972</t>
+          <t>342232</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>43477</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3809,17 +3793,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABIGAIL </t>
+          <t xml:space="preserve">AXEL ANTONIO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t xml:space="preserve">JIMENEZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>BALDERAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3829,79 +3813,67 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8122210747</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>SIERRA MADRE 453</t>
-        </is>
-      </c>
+          <t>8120371548</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-02-1994</t>
+          <t>09-10-2007</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALIRODJZ@GMAIL.COM</t>
+          <t>AXEL.JB@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15-07-2024 17:42:01</t>
+          <t>09-02-2026 16:00:49</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>18-02-2026 17:35:03</t>
+          <t>12-02-2026 19:04:39</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>18-02-2026 17:34:11</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3909,36 +3881,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26180522469530005149</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26180522303960004480</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>296202</t>
+          <t>342249</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93700</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,17 +3928,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t>WENDY PATRICIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>SUÁREZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3968,67 +3948,75 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8681587267</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>8127640011</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>METROPLEX</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>06-01-1996</t>
+          <t>11-10-1999</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ERICK.BRAVO2006@HOTMAIL.COM</t>
+          <t>WENDYSUAREZ739@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-06-2025 04:58:16</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:21:10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-02-2026 03:31:46</t>
+          <t>09-02-2026 16:32:07</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-02-2026 16:30:42</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4036,19 +4024,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26180522024080003151</t>
+          <t>26180522198510003955</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4060,12 +4048,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>325652</t>
+          <t>245972</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>43477</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4075,17 +4063,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CÉSAR JOSUE</t>
+          <t xml:space="preserve">ABIGAIL </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,35 +4083,39 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8111069963</t>
+          <t>8122210747</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RIO MOCTEZUMA 124</t>
+          <t>SIERRA MADRE 453</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-07-1993</t>
+          <t>28-02-1994</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CTREJOTELLO@GMAIL.COM</t>
+          <t>ALIRODJZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>27-11-2025 14:55:58</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>15-07-2024 17:42:01</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4141,17 +4133,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>12-02-2026 10:44:53</t>
+          <t>18-02-2026 17:35:03</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>12-02-2026 10:44:03</t>
+          <t>18-02-2026 17:34:11</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4161,7 +4153,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4171,19 +4163,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26180522291040004389</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522469530005149</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4191,24 +4175,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342076</t>
+          <t>296202</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>93700</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4218,17 +4202,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4238,14 +4222,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8135890269</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>SIERRA DE MORTEROS 4032</t>
-        </is>
-      </c>
+          <t>8681587267</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4253,60 +4233,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24-06-1958</t>
+          <t>06-01-1996</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JM8107473@GMAIL.COM</t>
+          <t>ERICK.BRAVO2006@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 09:46:18</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>03-06-2025 04:58:16</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 09:54:15</t>
+          <t>03-02-2026 03:31:46</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>09-02-2026 09:52:42</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4314,14 +4290,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26180522187000003875</t>
+          <t>26180522024080003151</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4338,12 +4314,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>339983</t>
+          <t>318392</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4353,17 +4329,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO</t>
+          <t xml:space="preserve">EDGAR ALEJANDRO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve"> BERNAL </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4373,12 +4349,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9618542444</t>
+          <t>8131546744</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SIERRA LOS NOGALES 748</t>
+          <t>CIRCUITO DE LOS ERUDITOS 1120</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4388,17 +4364,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22-03-2002</t>
+          <t>27-10-1992</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>AGULAR.MORALES.L.E@GMAIL.COM</t>
+          <t>EDGARCANTU.B@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 09:59:16</t>
+          <t>13-10-2025 08:26:51</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4419,7 +4395,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 10:04:51</t>
+          <t>02-02-2026 10:14:11</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4429,7 +4405,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-02-2026 10:03:44</t>
+          <t>02-02-2026 10:13:38</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4449,11 +4425,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26180522004150003068</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+          <t>26180522004370003069</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>499</t>
@@ -4461,7 +4445,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4473,12 +4457,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>339863</t>
+          <t>342076</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4488,17 +4472,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CARMEN ALONDRA</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ZURITA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4508,67 +4492,75 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8131040948</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>8135890269</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SIERRA DE MORTEROS 4032</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-02-2006</t>
+          <t>24-06-1958</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALONDRAZG527@GMAIL.COM</t>
+          <t>JM8107473@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-02-2026 06:15:16</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 09:46:18</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-02-2026 06:16:26</t>
+          <t>09-02-2026 09:54:15</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>09-02-2026 09:52:42</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4576,19 +4568,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26180521998280003041</t>
+          <t>26180522187000003875</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4600,12 +4592,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>339865</t>
+          <t>339863</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,17 +4607,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>CARMEN ALONDRA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SEPTIMO</t>
+          <t>ZURITA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BALLINAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4635,7 +4627,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8128909829</t>
+          <t>8131040948</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4646,17 +4638,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16-11-2006</t>
+          <t>15-02-2006</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>FERSEPTIMO66@GMAIL.COM</t>
+          <t>ALONDRAZG527@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-02-2026 06:18:29</t>
+          <t>02-02-2026 06:15:16</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4681,7 +4673,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 06:19:40</t>
+          <t>02-02-2026 06:16:26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4703,7 +4695,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26180521998420003042</t>
+          <t>26180521998280003041</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4727,12 +4719,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342232</t>
+          <t>339865</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4742,17 +4734,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AXEL ANTONIO </t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENEZ </t>
+          <t>SEPTIMO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BALDERAS</t>
+          <t>BALLINAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4762,28 +4754,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8120371548</t>
+          <t>8128909829</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>09-10-2007</t>
+          <t>16-11-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>AXEL.JB@OUTLOOK.COM</t>
+          <t>FERSEPTIMO66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 16:00:49</t>
+          <t>02-02-2026 06:18:29</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4808,12 +4800,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12-02-2026 19:04:39</t>
+          <t>02-02-2026 06:19:40</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4830,19 +4822,11 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26180522303960004480</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180521998420003042</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>549</t>
@@ -4850,7 +4834,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4862,12 +4846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342249</t>
+          <t>340074</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4877,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WENDY PATRICIA</t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SUÁREZ</t>
+          <t>YERVES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4897,14 +4881,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8127640011</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>METROPLEX</t>
-        </is>
-      </c>
+          <t>8333266247</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4912,60 +4892,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11-10-1999</t>
+          <t>05-10-1992</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>WENDYSUAREZ739@GMAIL.COM</t>
+          <t>THEREYRBZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 16:21:10</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>02-02-2026 11:58:17</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 16:32:07</t>
+          <t>11-02-2026 15:47:00</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>09-02-2026 16:30:42</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4973,14 +4949,22 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26180522198510003955</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26180522267110004278</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4997,12 +4981,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341966</t>
+          <t>342168</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5012,17 +4996,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IDALIA YAZMIN</t>
+          <t>KEVIN MIGUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>ALFARO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ESCALANTE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5032,32 +5016,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8180197129</t>
+          <t>8126005764</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SAN GREGORIO</t>
+          <t>BOSQUE DE ABEDULES 642</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18-09-1996</t>
+          <t>30-09-2002</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>YAZMINORTIZ607@GMAIL.COM</t>
+          <t>KEVINMIGUELALFARODIAZ2002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>08-02-2026 15:54:09</t>
+          <t>09-02-2026 13:57:17</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5078,7 +5062,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 19:30:00</t>
+          <t>09-02-2026 14:12:38</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5088,7 +5072,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:58</t>
+          <t>09-02-2026 14:11:08</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5098,7 +5082,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5108,10 +5092,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26180522223570004057</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
+          <t>26180522192670003905</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5120,7 +5108,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Aurora Nohemi Juarez Garza</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5132,12 +5120,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340074</t>
+          <t>339753</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5147,17 +5135,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>FEDERICO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>YERVES</t>
+          <t xml:space="preserve"> AMARO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5167,67 +5155,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8333266247</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>8131096958</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10 DE MAYO 187</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>05-10-1992</t>
+          <t>22-05-1994</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>THEREYRBZ@GMAIL.COM</t>
+          <t>AMARODAVILA377@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 11:58:17</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 09:47:57</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:47:00</t>
+          <t>01-02-2026 09:54:01</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>01-02-2026 09:51:56</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5235,27 +5231,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26180522267110004278</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180521988280003004</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5267,12 +5255,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342168</t>
+          <t>341966</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5282,17 +5270,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KEVIN MIGUEL</t>
+          <t>IDALIA YAZMIN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ALFARO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ESCALANTE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5302,32 +5290,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8126005764</t>
+          <t>8180197129</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BOSQUE DE ABEDULES 642</t>
+          <t>SAN GREGORIO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30-09-2002</t>
+          <t>18-09-1996</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>KEVINMIGUELALFARODIAZ2002@GMAIL.COM</t>
+          <t>YAZMINORTIZ607@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 13:57:17</t>
+          <t>08-02-2026 15:54:09</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5348,7 +5336,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 14:12:38</t>
+          <t>09-02-2026 19:30:00</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5358,7 +5346,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>09-02-2026 14:11:08</t>
+          <t>09-02-2026 17:23:58</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5368,7 +5356,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5378,14 +5366,10 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26180522192670003905</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522223570004057</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
@@ -5394,7 +5378,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Aurora Nohemi Juarez Garza</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5406,12 +5390,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342201</t>
+          <t>325652</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5421,17 +5405,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>CÉSAR JOSUE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5441,10 +5425,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8121490904</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>8111069963</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RIO MOCTEZUMA 124</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5452,56 +5440,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>05-03-2009</t>
+          <t>23-07-1993</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ALEJANDRO.MTZDAVILA5@GMAIL.COM</t>
+          <t>CTREJOTELLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:01:11</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>27-11-2025 14:55:58</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:57</t>
+          <t>12-02-2026 10:44:53</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>12-02-2026 10:44:03</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5509,19 +5501,27 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26180522194600003915</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26180522291040004389</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5533,12 +5533,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>340571</t>
+          <t>342544</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRHISTIAN RAUL</t>
+          <t>FATIMA JAMILETH</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RAYON</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5568,28 +5568,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8131125081</t>
+          <t>8181377067</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27-07-2007</t>
+          <t>20-07-2007</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CRHISTIANMENDEZ66@GMAIL.COM</t>
+          <t>CARRILLOJAMILETH659@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>03-02-2026 13:34:36</t>
+          <t>10-02-2026 08:07:32</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-02-2026 13:35:35</t>
+          <t>10-02-2026 08:09:12</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26180522039850003222</t>
+          <t>26180522225160004069</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5660,12 +5660,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342544</t>
+          <t>342201</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FATIMA JAMILETH</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5695,28 +5695,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8181377067</t>
+          <t>8121490904</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20-07-2007</t>
+          <t>05-03-2009</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CARRILLOJAMILETH659@GMAIL.COM</t>
+          <t>ALEJANDRO.MTZDAVILA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-02-2026 08:07:32</t>
+          <t>09-02-2026 15:01:11</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5741,18 +5741,18 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 08:09:12</t>
+          <t>09-02-2026 15:05:57</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26180522225160004069</t>
+          <t>26180522194600003915</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5787,12 +5787,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342314</t>
+          <t>339983</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZIEL RAUL </t>
+          <t>LUIS EDUARDO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8116392285</t>
+          <t>9618542444</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SAN GILBERTO</t>
+          <t>SIERRA LOS NOGALES 748</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>09-08-1989</t>
+          <t>22-03-2002</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>OZIEL89@HOTMAIL.COM</t>
+          <t>AGULAR.MORALES.L.E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:18:43</t>
+          <t>02-02-2026 09:59:16</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5868,17 +5868,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:44</t>
+          <t>02-02-2026 10:04:51</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:16</t>
+          <t>02-02-2026 10:03:44</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26180522201820003970</t>
+          <t>26180522004150003068</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5922,12 +5922,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340924</t>
+          <t>343535</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO  </t>
+          <t xml:space="preserve">VALENTINA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2461048821</t>
+          <t>8181797114</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SAN ELIAS 728</t>
+          <t>OASIS DE OMAN 315</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28-10-1992</t>
+          <t>27-12-2002</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>FERSALAMANCA92@GMAIL.COM</t>
+          <t>VALE27CRISTOBAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>04-02-2026 09:59:48</t>
+          <t>13-02-2026 16:43:48</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6003,17 +6003,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>12-02-2026 18:00:00</t>
+          <t>13-02-2026 16:47:24</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:20</t>
+          <t>13-02-2026 16:46:56</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26180522301070004465</t>
+          <t>26180522324830004561</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6327,12 +6327,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342664</t>
+          <t>342314</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6342,17 +6342,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR ALEJANDRO </t>
+          <t xml:space="preserve">OZIEL RAUL </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6141396095</t>
+          <t>8116392285</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASTORGA </t>
+          <t>SAN GILBERTO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6377,17 +6377,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>25-04-1983</t>
+          <t>09-08-1989</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>OMARTORRES2504@HOTMAIL.COM</t>
+          <t>OZIEL89@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:22</t>
+          <t>09-02-2026 17:18:43</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6408,17 +6408,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 16:30:00</t>
+          <t>09-02-2026 17:21:44</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>12-02-2026 15:15:02</t>
+          <t>09-02-2026 17:21:16</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6438,19 +6438,11 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26180522298000004448</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522201820003970</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
           <t>499</t>
@@ -6613,12 +6605,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>340569</t>
+          <t>340571</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18387</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6628,17 +6620,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CARLOS ALEJANDRO</t>
+          <t>CRHISTIAN RAUL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NIÑO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>RAYON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6648,7 +6640,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8115530627</t>
+          <t>8131125081</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6659,17 +6651,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>04-07-2006</t>
+          <t>27-07-2007</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CARLOSLAVARDO040706@GMAIL.COM</t>
+          <t>CRHISTIANMENDEZ66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>03-02-2026 13:31:45</t>
+          <t>03-02-2026 13:34:36</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6694,7 +6686,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>03-02-2026 13:32:42</t>
+          <t>03-02-2026 13:35:35</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6716,7 +6708,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26180522039810003221</t>
+          <t>26180522039850003222</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6740,12 +6732,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343535</t>
+          <t>342664</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6755,17 +6747,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENTINA </t>
+          <t xml:space="preserve">OMAR ALEJANDRO </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6775,32 +6767,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8181797114</t>
+          <t>6141396095</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>OASIS DE OMAN 315</t>
+          <t xml:space="preserve">ASTORGA </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>27-12-2002</t>
+          <t>25-04-1983</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>VALE27CRISTOBAL@GMAIL.COM</t>
+          <t>OMARTORRES2504@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13-02-2026 16:43:48</t>
+          <t>10-02-2026 15:16:22</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6821,17 +6813,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>13-02-2026 16:47:24</t>
+          <t>12-02-2026 16:30:00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13-02-2026 16:46:56</t>
+          <t>12-02-2026 15:15:02</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6851,11 +6843,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26180522324830004561</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>26180522298000004448</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>499</t>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6875,12 +6875,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>344175</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6890,17 +6890,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HANNA MARIVI</t>
+          <t>NERY GAEL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6910,48 +6910,48 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8135670542</t>
+          <t>8186034704</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JARDINES </t>
+          <t>VIÑEDO ITALIANO</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>02-04-2002</t>
+          <t>14-10-2003</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>HANNASALAZAR.240419@GMAIL.COM</t>
+          <t>MILKOMEDA2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>12-02-2026 16:40:10</t>
+          <t>16-02-2026 16:46:46</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>949</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>16-02-2026 16:30:42</t>
+          <t>16-02-2026 17:06:50</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6986,22 +6986,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26180522419670004906</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522419840004908</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>949</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7018,12 +7010,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342969</t>
+          <t>343317</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7033,17 +7025,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JOSSAFAT EMMANUEL</t>
+          <t>HANNA MARIVI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7053,32 +7045,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8123907995</t>
+          <t>8135670542</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>RIO SERRANO 112</t>
+          <t xml:space="preserve">JARDINES </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>26-03-2009</t>
+          <t>02-04-2002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ERR563833@GMAIL.COM</t>
+          <t>HANNASALAZAR.240419@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>11-02-2026 13:04:40</t>
+          <t>12-02-2026 16:40:10</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7094,22 +7086,22 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>13-02-2026 18:29:51</t>
+          <t>17-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>13-02-2026 18:24:25</t>
+          <t>16-02-2026 16:30:42</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7129,40 +7121,44 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26180522328290004593</t>
+          <t>26180522419670004906</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>341614</t>
+          <t>340924</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7172,17 +7168,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>XIMENA ALEJANDRA</t>
+          <t xml:space="preserve">FERNANDO  </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SALAMANCA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7192,32 +7188,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6144578497</t>
+          <t>2461048821</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ASTORGA 322</t>
+          <t>SAN ELIAS 728</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15-06-2012</t>
+          <t>28-10-1992</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>XIMENATORRES150212@GMAIL.COM</t>
+          <t>FERSALAMANCA92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>06-02-2026 16:02:10</t>
+          <t>04-02-2026 09:59:48</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7238,17 +7234,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10-02-2026 15:25:06</t>
+          <t>12-02-2026 18:00:00</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>10-02-2026 15:24:27</t>
+          <t>12-02-2026 17:57:20</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7268,19 +7264,11 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26180522234410004112</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522301070004465</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
           <t>499</t>
@@ -7288,7 +7276,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7300,12 +7288,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>340574</t>
+          <t>340569</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7315,17 +7303,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FRANCISCO JOEL</t>
+          <t>CARLOS ALEJANDRO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>NIÑO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RODEA</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7335,7 +7323,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8126312778</t>
+          <t>8115530627</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7346,17 +7334,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>09-03-2007</t>
+          <t>04-07-2006</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>FRAN2209YF@GMAIL.COM</t>
+          <t>CARLOSLAVARDO040706@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>03-02-2026 13:37:26</t>
+          <t>03-02-2026 13:31:45</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7381,7 +7369,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-02-2026 13:38:17</t>
+          <t>03-02-2026 13:32:42</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7403,7 +7391,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26180522039920003223</t>
+          <t>26180522039810003221</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7415,7 +7403,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7427,12 +7415,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343515</t>
+          <t>340574</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7442,17 +7430,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BRAYAN DAVID</t>
+          <t>FRANCISCO JOEL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>RODEA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7462,14 +7450,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8134505125</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>RIO TAMUIN 158</t>
-        </is>
-      </c>
+          <t>8126312778</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7477,60 +7461,56 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01-11-1996</t>
+          <t>09-03-2007</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>GZZD539@GMAIL.COM</t>
+          <t>FRAN2209YF@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>13-02-2026 15:33:17</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>03-02-2026 13:37:26</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>13-02-2026 15:38:37</t>
+          <t>03-02-2026 13:38:17</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>13-02-2026 15:37:08</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7538,19 +7518,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26180522322900004547</t>
+          <t>26180522039920003223</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7562,12 +7542,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>342969</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7577,17 +7557,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JARED MANASÉS</t>
+          <t>JOSSAFAT EMMANUEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERNÁNDEZ</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7597,10 +7577,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9511939543</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>8123907995</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RIO SERRANO 112</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7608,56 +7592,60 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>05-07-2005</t>
+          <t>26-03-2009</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>MARCIALJARIS@GMAIL.COM</t>
+          <t>ERR563833@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>07-02-2026 21:58:54</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 13:04:40</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>09-02-2026 18:25:04</t>
+          <t>13-02-2026 18:29:51</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13-02-2026 18:24:25</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7665,7 +7653,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26180522207000003988</t>
+          <t>26180522328290004593</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7676,29 +7664,29 @@
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344175</t>
+          <t>343515</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7708,17 +7696,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NERY GAEL</t>
+          <t>BRAYAN DAVID</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7728,12 +7716,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8186034704</t>
+          <t>8134505125</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>VIÑEDO ITALIANO</t>
+          <t>RIO TAMUIN 158</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7743,48 +7731,48 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>14-10-2003</t>
+          <t>01-11-1996</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>MILKOMEDA2003@GMAIL.COM</t>
+          <t>GZZD539@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 16:46:46</t>
+          <t>13-02-2026 15:33:17</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>17-02-2026 08:00:00</t>
+          <t>13-02-2026 15:38:37</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:06:50</t>
+          <t>13-02-2026 15:37:08</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7804,36 +7792,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26180522419840004908</t>
+          <t>26180522322900004547</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344285</t>
+          <t>341984</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7843,17 +7831,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARICRUZ </t>
+          <t>EVER ALBERTO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ESCOBEDO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7863,79 +7851,67 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8110441305</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>SANTA CATARINA</t>
-        </is>
-      </c>
+          <t>8184026331</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>01-07-1997</t>
+          <t>13-02-2010</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>MTZMARICRUZ31@GMAIL.COM</t>
+          <t>EVERVZZESCOBEDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 18:27:29</t>
+          <t>09-02-2026 03:45:57</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 18:31:22</t>
+          <t>09-02-2026 03:48:37</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:30:30</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7943,19 +7919,27 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26180522404740004848</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
+          <t>26180522173570003850</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7967,12 +7951,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>341984</t>
+          <t>344285</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7982,17 +7966,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EVER ALBERTO</t>
+          <t xml:space="preserve">MARICRUZ </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ESCOBEDO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8002,67 +7986,79 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8184026331</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>8110441305</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SANTA CATARINA</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>13-02-2010</t>
+          <t>01-07-1997</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>EVERVZZESCOBEDO@GMAIL.COM</t>
+          <t>MTZMARICRUZ31@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 03:45:57</t>
+          <t>16-02-2026 18:27:29</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>09-02-2026 03:48:37</t>
+          <t>16-02-2026 18:31:22</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:30:30</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8070,27 +8066,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26180522173570003850</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>LILIANA SARAHI MORALES VARGAS</t>
-        </is>
-      </c>
+          <t>26180522404740004848</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8237,12 +8225,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343559</t>
+          <t>342242</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8252,17 +8240,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARTURO </t>
+          <t>EVA MARIANA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MAGALLANES</t>
+          <t>MAYA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8272,39 +8260,35 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8115902527</t>
+          <t>8134495854</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MEXICO 225</t>
+          <t>METROPLEX</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>10-08-1987</t>
+          <t>17-03-1998</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ORUTRA.MAGALLANES@GMAIL.COM</t>
+          <t>MARIANAMAYARDZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>13-02-2026 17:20:36</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:10:28</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8322,17 +8306,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 17:25:01</t>
+          <t>09-02-2026 16:23:15</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>16-02-2026 17:24:02</t>
+          <t>09-02-2026 16:22:54</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8342,7 +8326,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8352,19 +8336,15 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26180522399260004814</t>
+          <t>26180522197900003949</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
           <t>499</t>
@@ -8372,7 +8352,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8384,12 +8364,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343630</t>
+          <t>341614</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8399,17 +8379,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KAREN DENISSE</t>
+          <t>XIMENA ALEJANDRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AQUINO</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8419,12 +8399,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8188683490</t>
+          <t>6144578497</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>HACIENDA SAN AGUSTIN 100</t>
+          <t>ASTORGA 322</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8434,17 +8414,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19-11-1993</t>
+          <t>15-06-2012</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>KAMEDINA1920@HOTMAIL.COM</t>
+          <t>XIMENATORRES150212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>14-02-2026 06:05:31</t>
+          <t>06-02-2026 16:02:10</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8465,17 +8445,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>14-02-2026 06:10:01</t>
+          <t>10-02-2026 15:25:06</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>14-02-2026 06:09:31</t>
+          <t>10-02-2026 15:24:27</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8485,7 +8465,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8495,11 +8475,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26180522332650004617</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
+          <t>26180522234410004112</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>499</t>
@@ -8507,24 +8495,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>342242</t>
+          <t>344065</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8534,17 +8522,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EVA MARIANA</t>
+          <t>JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MAYA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8554,12 +8542,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8134495854</t>
+          <t>8117232420</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>METROPLEX</t>
+          <t>RIO ATOYA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8569,20 +8557,24 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17-03-1998</t>
+          <t>23-12-1991</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MARIANAMAYARDZ@GMAIL.COM</t>
+          <t>AROMELY_23@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>09-02-2026 16:10:28</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>16-02-2026 13:19:23</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8600,17 +8592,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>09-02-2026 16:23:15</t>
+          <t>16-02-2026 13:24:31</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>09-02-2026 16:22:54</t>
+          <t>16-02-2026 13:23:46</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8620,7 +8612,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8630,14 +8622,10 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26180522197900003949</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522388570004746</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
@@ -8646,7 +8634,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -8658,12 +8646,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344065</t>
+          <t>343559</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8673,17 +8661,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JESSICA ELIZABETH</t>
+          <t xml:space="preserve">ARTURO </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>MAGALLANES</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESPARZA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8693,32 +8681,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8117232420</t>
+          <t>8115902527</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>RIO ATOYA</t>
+          <t>MEXICO 225</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>23-12-1991</t>
+          <t>10-08-1987</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>AROMELY_23@OUTLOOK.COM</t>
+          <t>ORUTRA.MAGALLANES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 13:19:23</t>
+          <t>13-02-2026 17:20:36</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8743,7 +8731,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 13:24:31</t>
+          <t>16-02-2026 17:25:01</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -8753,7 +8741,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>16-02-2026 13:23:46</t>
+          <t>16-02-2026 17:24:02</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8773,11 +8761,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26180522388570004746</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>26180522399260004814</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>499</t>
@@ -8785,7 +8781,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8797,12 +8793,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>345086</t>
+          <t>343630</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>87251</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8812,17 +8808,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JHONJAIRO</t>
+          <t>KAREN DENISSE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>AQUINO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8832,39 +8828,35 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8112289625</t>
+          <t>8188683490</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TOBOSOS 101</t>
+          <t>HACIENDA SAN AGUSTIN 100</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16-02-2006</t>
+          <t>19-11-1993</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>JHONJAIRODIAZ61@GMAIL.COM</t>
+          <t>KAMEDINA1920@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>19-02-2026 15:00:58</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>14-02-2026 06:05:31</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8882,17 +8874,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>19-02-2026 15:05:11</t>
+          <t>14-02-2026 06:10:01</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>19-02-2026 15:04:37</t>
+          <t>14-02-2026 06:09:31</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8902,7 +8894,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8912,7 +8904,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26180522496050005244</t>
+          <t>26180522332650004617</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -8936,12 +8928,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>342806</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8951,17 +8943,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MANUEL ALBERTO</t>
+          <t>JARED MANASÉS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CURIQUEO</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>HERNÁNDEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8971,7 +8963,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8126387214</t>
+          <t>9511939543</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8982,17 +8974,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31-01-1995</t>
+          <t>05-07-2005</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>MANUCCQUEO@GMAIL.COM</t>
+          <t>MARCIALJARIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>10-02-2026 18:38:14</t>
+          <t>07-02-2026 21:58:54</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9007,17 +8999,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10-02-2026 18:40:47</t>
+          <t>09-02-2026 18:25:04</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -9039,36 +9031,40 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26180522244290004176</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
+          <t>26180522207000003988</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345088</t>
+          <t>345086</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87253</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9078,17 +9074,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO </t>
+          <t>JHONJAIRO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9098,12 +9094,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8119638301</t>
+          <t>8112289625</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>HACIENDA DEL FRESNO 110</t>
+          <t>TOBOSOS 101</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9113,17 +9109,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>30-09-2006</t>
+          <t>16-02-2006</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>RICARDO.ROJAS9920@ICLOUD.COM</t>
+          <t>JHONJAIRODIAZ61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19-02-2026 15:09:00</t>
+          <t>19-02-2026 15:00:58</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9148,7 +9144,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>19-02-2026 15:13:05</t>
+          <t>19-02-2026 15:05:11</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -9158,7 +9154,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19-02-2026 15:12:37</t>
+          <t>19-02-2026 15:04:37</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9178,7 +9174,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26180522496250005246</t>
+          <t>26180522496050005244</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9329,12 +9325,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>345118</t>
+          <t>345088</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>87283</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9344,17 +9340,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HECTOR MAURICIO</t>
+          <t xml:space="preserve">RICARDO </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GARIBAY</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9364,53 +9360,57 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8181810051</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>8119638301</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>HACIENDA DEL FRESNO 110</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>14-01-1997</t>
+          <t>30-09-2006</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>MAURICIO.MTZG@HOTMAIL.COM</t>
+          <t>RICARDO.ROJAS9920@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>19-02-2026 16:07:08</t>
+          <t>19-02-2026 15:09:00</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>19-02-2026 16:08:57</t>
+          <t>19-02-2026 15:13:05</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -9418,13 +9418,21 @@
           <t>19-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:12:37</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9432,14 +9440,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26180522498220005267</t>
+          <t>26180522496250005246</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9718,12 +9726,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>342781</t>
+          <t>345937</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>88102</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9733,17 +9741,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>URIEL ALEXIS</t>
+          <t>ADELFA GABRIELA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9753,35 +9761,39 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8714096491</t>
+          <t>8120265470</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CRISTOBAL COLON 522</t>
+          <t>SIERRA DEL ESPINAZO 1113</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20-09-1993</t>
+          <t>10-03-2004</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>URIELMTZREY@GMAIL.COM</t>
+          <t>GF961430@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>10-02-2026 18:10:02</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>23-02-2026 17:44:31</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9799,17 +9811,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-02-2026 18:14:21</t>
+          <t>23-02-2026 17:49:59</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>10-02-2026 18:13:50</t>
+          <t>23-02-2026 17:49:01</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9829,7 +9841,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26180522242810004167</t>
+          <t>26180522592650005629</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
@@ -9841,24 +9853,24 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>344176</t>
+          <t>345118</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9868,17 +9880,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MARIO CESAR</t>
+          <t>HECTOR MAURICIO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>GARIBAY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9888,32 +9900,28 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8125930595</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>VIÑEDO ITALIANO</t>
-        </is>
-      </c>
+          <t>8181810051</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>25-09-2001</t>
+          <t>14-01-1997</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>GAZERSERENITY@GMAIL.COM</t>
+          <t>MAURICIO.MTZG@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>16-02-2026 16:46:48</t>
+          <t>19-02-2026 16:07:08</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -9923,44 +9931,36 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>16-02-2026 17:14:56</t>
+          <t>19-02-2026 16:08:57</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:14:29</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9968,14 +9968,14 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26180522398330004810</t>
+          <t>26180522498220005267</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -9992,12 +9992,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>344473</t>
+          <t>342806</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10007,17 +10007,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>MANUEL ALBERTO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CURIQUEO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8119077656</t>
+          <t>8126387214</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10038,17 +10038,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>04-02-2008</t>
+          <t>31-01-1995</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>RODRIGO.INSTAPIC@GMAIL.COM</t>
+          <t>MANUCCQUEO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>17-02-2026 13:03:56</t>
+          <t>10-02-2026 18:38:14</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10063,28 +10063,28 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>17-02-2026 13:04:47</t>
+          <t>10-02-2026 18:40:47</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V72" t="inlineStr"/>
@@ -10095,19 +10095,19 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26180522427280004929</t>
+          <t>26180522244290004176</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10119,12 +10119,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344575</t>
+          <t>342781</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10134,17 +10134,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>URIEL ALEXIS</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10154,67 +10154,75 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8154541233</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>8714096491</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CRISTOBAL COLON 522</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>30-10-1983</t>
+          <t>20-09-1993</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>GABB301083@GMAIL.COM</t>
+          <t>URIELMTZREY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>17-02-2026 16:43:36</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 18:10:02</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>17-02-2026 16:45:26</t>
+          <t>10-02-2026 18:14:21</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>10-02-2026 18:13:50</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10222,19 +10230,19 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26180522435020004990</t>
+          <t>26180522242810004167</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -10512,12 +10520,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344101</t>
+          <t>344176</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10527,17 +10535,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PATRICIO</t>
+          <t>MARIO CESAR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10547,12 +10555,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8186800359</t>
+          <t>8125930595</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CALLE ALTOCUMULUS 310</t>
+          <t>VIÑEDO ITALIANO</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10562,17 +10570,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>16-08-2003</t>
+          <t>25-09-2001</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>PATRICIOHDZ2009@HOTMAIL.COM</t>
+          <t>GAZERSERENITY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>16-02-2026 14:43:09</t>
+          <t>16-02-2026 16:46:48</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10587,27 +10595,27 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>19-02-2026 15:15:54</t>
+          <t>16-02-2026 17:14:56</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>19-02-2026 15:15:11</t>
+          <t>16-02-2026 17:14:29</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10617,7 +10625,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10627,18 +10635,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26180522496340005247</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522398330004810</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10655,12 +10659,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344880</t>
+          <t>344101</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10670,17 +10674,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>PATRICIO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10690,28 +10694,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8129128953</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>8186800359</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>CALLE ALTOCUMULUS 310</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>16-08-2003</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>VALERIAROGELHDZ@GMAIL.COM</t>
+          <t>PATRICIOHDZ2009@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18-02-2026 16:58:52</t>
+          <t>16-02-2026 14:43:09</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10721,36 +10729,44 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>18-02-2026 17:00:33</t>
+          <t>19-02-2026 15:15:54</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:15:11</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10758,36 +10774,40 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26180522467780005133</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr"/>
+          <t>26180522496340005247</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>345302</t>
+          <t>344473</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>87467</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10797,17 +10817,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACISCO JAVIER </t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MORIN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10817,7 +10837,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8114668597</t>
+          <t>8119077656</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10828,20 +10848,24 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>04-02-2008</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>FRANCISTOTI88@GMAIL.COM</t>
+          <t>RODRIGO.INSTAPIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>20-02-2026 15:17:35</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>17-02-2026 13:03:56</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10849,28 +10873,28 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>20-02-2026 15:20:10</t>
+          <t>17-02-2026 13:04:47</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>20-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V78" t="inlineStr"/>
@@ -10881,22 +10905,399 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26180522528270005374</t>
+          <t>26180522427280004929</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>344575</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>22392</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GABRIELA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CISNEROS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CISNEROS</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>8154541233</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>30-10-1983</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>GABB301083@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:43:36</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:45:26</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>26180522435020004990</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>344880</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>22697</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VALERIA</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ROGEL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>8129128953</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>21-11-2007</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>VALERIAROGELHDZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:58:52</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>18-02-2026 17:00:33</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>26180522467780005133</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>345302</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>87467</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRACISCO JAVIER </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LARA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MORIN</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>8114668597</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>01-10-2003</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>FRANCISTOTI88@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>20-02-2026 15:17:35</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>20-02-2026 15:20:10</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>20-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>26180522528270005374</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -2571,12 +2571,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>239891</t>
+          <t>316119</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR AZAEL </t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABURTO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2606,10 +2606,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8189633349</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>8125770715</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PAMPLONA</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2617,56 +2621,60 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>09-06-2009</t>
+          <t>03-11-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CADA090909CESAR@GMAIL.COM</t>
+          <t>WILLIAM.RODRIGUEZ@UNIAM.EDU.MX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14-06-2024 19:41:16</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>28-09-2025 19:31:41</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 14:21:46</t>
+          <t>02-02-2026 15:08:37</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:07:57</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2674,14 +2682,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522075620003383</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26180522013870003124</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2698,12 +2710,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>298061</t>
+          <t>318215</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>95559</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2713,17 +2725,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DAVID OZIEL</t>
+          <t>PERLA JAZMIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RINCON</t>
+          <t>EMILIANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERLANGA </t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2733,67 +2745,75 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8113134704</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>8119127750</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SANTA CATARINA</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-08-2010</t>
+          <t>10-05-1989</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DAVIDOZIELRINCONB@GMAIL.COM</t>
+          <t>JAZZGALVAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12-06-2025 15:05:36</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-10-2025 07:14:32</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>18-02-2026 17:16:52</t>
+          <t>09-02-2026 18:01:44</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:01:13</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2801,7 +2821,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26180522468690005145</t>
+          <t>26180522205010003980</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2812,7 +2832,7 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2829,12 +2849,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>316119</t>
+          <t>239891</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2844,17 +2864,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WILLIAM</t>
+          <t xml:space="preserve">CESAR AZAEL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ABURTO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2864,14 +2884,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8125770715</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>PAMPLONA</t>
-        </is>
-      </c>
+          <t>8189633349</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2879,60 +2895,56 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-11-2008</t>
+          <t>09-06-2009</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>WILLIAM.RODRIGUEZ@UNIAM.EDU.MX</t>
+          <t>CADA090909CESAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>28-09-2025 19:31:41</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>14-06-2024 19:41:16</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 15:08:37</t>
+          <t>04-02-2026 14:21:46</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:07:57</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2940,18 +2952,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26180522013870003124</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522075620003383</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2968,12 +2976,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>318215</t>
+          <t>298061</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>95559</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2983,17 +2991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PERLA JAZMIN</t>
+          <t>DAVID OZIEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EMILIANO</t>
+          <t>RINCON</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">BERLANGA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3003,75 +3011,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8119127750</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>SANTA CATARINA</t>
-        </is>
-      </c>
+          <t>8113134704</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10-05-1989</t>
+          <t>06-08-2010</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JAZZGALVAE@GMAIL.COM</t>
+          <t>DAVIDOZIELRINCONB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11-10-2025 07:14:32</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>12-06-2025 15:05:36</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:44</t>
+          <t>18-02-2026 17:16:52</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:01:13</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26180522205010003980</t>
+          <t>26180522468690005145</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3090,7 +3090,7 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -4060,12 +4060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>339753</t>
+          <t>339863</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FEDERICO</t>
+          <t>CARMEN ALONDRA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AMARO</t>
+          <t>ZURITA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,75 +4095,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8131096958</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10 DE MAYO 187</t>
-        </is>
-      </c>
+          <t>8131040948</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-05-1994</t>
+          <t>15-02-2006</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AMARODAVILA377@GMAIL.COM</t>
+          <t>ALONDRAZG527@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>01-02-2026 09:47:57</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>02-02-2026 06:15:16</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>01-02-2026 09:54:01</t>
+          <t>02-02-2026 06:16:26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>01-02-2026 09:51:56</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4171,19 +4163,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26180521988280003004</t>
+          <t>26180521998280003041</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4195,12 +4187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>325652</t>
+          <t>339865</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,17 +4202,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CESAR JOSUE</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>SEPTIMO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>BALLINAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4230,75 +4222,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8111069963</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>RIO MOCTEZUMA 124</t>
-        </is>
-      </c>
+          <t>8128909829</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>23-07-1993</t>
+          <t>16-11-2006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CTREJOTELLO@GMAIL.COM</t>
+          <t>FERSEPTIMO66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>27-11-2025 14:55:58</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>02-02-2026 06:18:29</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-02-2026 10:44:53</t>
+          <t>02-02-2026 06:19:40</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>12-02-2026 10:44:03</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4306,27 +4290,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26180522291040004389</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180521998420003042</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4338,12 +4314,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>339863</t>
+          <t>339753</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4353,17 +4329,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CARMEN ALONDRA</t>
+          <t>FEDERICO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ZURITA</t>
+          <t xml:space="preserve"> AMARO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4373,67 +4349,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8131040948</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>8131096958</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10 DE MAYO 187</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15-02-2006</t>
+          <t>22-05-1994</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ALONDRAZG527@GMAIL.COM</t>
+          <t>AMARODAVILA377@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 06:15:16</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 09:47:57</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 06:16:26</t>
+          <t>01-02-2026 09:54:01</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>01-02-2026 09:51:56</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4441,19 +4425,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26180521998280003041</t>
+          <t>26180521988280003004</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4465,12 +4449,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>339865</t>
+          <t>325652</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4480,17 +4464,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>CESAR JOSUE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SEPTIMO</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BALLINAS</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4500,67 +4484,75 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8128909829</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>8111069963</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RIO MOCTEZUMA 124</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16-11-2006</t>
+          <t>23-07-1993</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FERSEPTIMO66@GMAIL.COM</t>
+          <t>CTREJOTELLO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-02-2026 06:18:29</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>27-11-2025 14:55:58</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-02-2026 06:19:40</t>
+          <t>12-02-2026 10:44:53</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>12-02-2026 10:44:03</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4568,19 +4560,27 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26180521998420003042</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26180522291040004389</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4727,12 +4727,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>339983</t>
+          <t>340074</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LUIS EDUARDO</t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>YERVES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4762,75 +4762,67 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9618542444</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SIERRA LOS NOGALES 748</t>
-        </is>
-      </c>
+          <t>8333266247</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-03-2002</t>
+          <t>05-10-1992</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>AGULAR.MORALES.L.E@GMAIL.COM</t>
+          <t>THEREYRBZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 09:59:16</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>02-02-2026 11:58:17</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 10:04:51</t>
+          <t>11-02-2026 15:47:00</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>02-02-2026 10:03:44</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4838,19 +4830,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26180522004150003068</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26180522267110004278</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4862,12 +4862,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341015</t>
+          <t>339983</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RAUL EDUARDO</t>
+          <t>LUIS EDUARDO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECHAVARRIA </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8134126486</t>
+          <t>9618542444</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VALLADOLID 3136</t>
+          <t>SIERRA LOS NOGALES 748</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>25-04-1996</t>
+          <t>22-03-2002</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EDUARDORAUL@GMAIL.COM</t>
+          <t>AGULAR.MORALES.L.E@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>04-02-2026 14:33:15</t>
+          <t>02-02-2026 09:59:16</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4943,17 +4943,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>04-02-2026 14:36:49</t>
+          <t>02-02-2026 10:04:51</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>04-02-2026 14:36:26</t>
+          <t>02-02-2026 10:03:44</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26180522076060003386</t>
+          <t>26180522004150003068</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4997,12 +4997,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341078</t>
+          <t>341015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>RAUL EDUARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CID</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t xml:space="preserve">ECHAVARRIA </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8180764767</t>
+          <t>8134126486</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CAÑON DE LA MIELERA 213</t>
+          <t>VALLADOLID 3136</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5047,17 +5047,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>14-11-1996</t>
+          <t>25-04-1996</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>XAVIERCID21@GMAIL.COM</t>
+          <t>EDUARDORAUL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>04-02-2026 16:35:12</t>
+          <t>04-02-2026 14:33:15</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>04-02-2026 16:43:33</t>
+          <t>04-02-2026 14:36:49</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>04-02-2026 16:40:54</t>
+          <t>04-02-2026 14:36:26</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26180522080330003428</t>
+          <t>26180522076060003386</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340074</t>
+          <t>341078</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5147,17 +5147,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>YERVES</t>
+          <t>CID</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CADENA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5167,67 +5167,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8333266247</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>8180764767</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CAÑON DE LA MIELERA 213</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>05-10-1992</t>
+          <t>14-11-1996</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>THEREYRBZ@GMAIL.COM</t>
+          <t>XAVIERCID21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 11:58:17</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 16:35:12</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 15:47:00</t>
+          <t>04-02-2026 16:43:33</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>04-02-2026 16:40:54</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5235,22 +5243,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26180522267110004278</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522080330003428</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5267,12 +5267,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340571</t>
+          <t>343535</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRHISTIAN RAUL</t>
+          <t xml:space="preserve">VALENTINA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RAYON</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5302,67 +5302,75 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8131125081</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>8181797114</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>OASIS DE OMAN 315</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>27-07-2007</t>
+          <t>27-12-2002</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CRHISTIANMENDEZ66@GMAIL.COM</t>
+          <t>VALE27CRISTOBAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>03-02-2026 13:34:36</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:43:48</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-02-2026 13:35:35</t>
+          <t>13-02-2026 16:47:24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:46:56</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5370,19 +5378,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26180522039850003222</t>
+          <t>26180522324830004561</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5394,12 +5402,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343535</t>
+          <t>340571</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5409,17 +5417,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENTINA </t>
+          <t>CRHISTIAN RAUL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>RAYON</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5429,75 +5437,67 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8181797114</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>OASIS DE OMAN 315</t>
-        </is>
-      </c>
+          <t>8131125081</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>27-12-2002</t>
+          <t>27-07-2007</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>VALE27CRISTOBAL@GMAIL.COM</t>
+          <t>CRHISTIANMENDEZ66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13-02-2026 16:43:48</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>03-02-2026 13:34:36</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>13-02-2026 16:47:24</t>
+          <t>03-02-2026 13:35:35</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:46:56</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5505,19 +5505,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26180522324830004561</t>
+          <t>26180522039850003222</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340924</t>
+          <t>344175</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO  </t>
+          <t>NERY GAEL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SALAMANCA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2461048821</t>
+          <t>8186034704</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SAN ELIAS 728</t>
+          <t>VIÑEDO ITALIANO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5722,48 +5722,48 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>28-10-1992</t>
+          <t>14-10-2003</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FERSALAMANCA92@GMAIL.COM</t>
+          <t>MILKOMEDA2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>04-02-2026 09:59:48</t>
+          <t>16-02-2026 16:46:46</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>949</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>12-02-2026 18:00:00</t>
+          <t>17-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:20</t>
+          <t>16-02-2026 17:06:50</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5783,14 +5783,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26180522301070004465</t>
+          <t>26180522419840004908</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>949</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5807,12 +5807,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344175</t>
+          <t>340924</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NERY GAEL</t>
+          <t xml:space="preserve">FERNANDO  </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SALAMANCA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8186034704</t>
+          <t>2461048821</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>VIÑEDO ITALIANO</t>
+          <t>SAN ELIAS 728</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5857,48 +5857,48 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14-10-2003</t>
+          <t>28-10-1992</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>MILKOMEDA2003@GMAIL.COM</t>
+          <t>FERSALAMANCA92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 16:46:46</t>
+          <t>04-02-2026 09:59:48</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-02-2026 08:00:00</t>
+          <t>12-02-2026 18:00:00</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>16-02-2026 17:06:50</t>
+          <t>12-02-2026 17:57:20</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5918,14 +5918,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26180522419840004908</t>
+          <t>26180522301070004465</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342544</t>
+          <t>341984</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6473,17 +6473,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FATIMA JAMILETH</t>
+          <t>EVER ALBERTO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MEJIA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>ESCOBEDO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6493,28 +6493,28 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8181377067</t>
+          <t>8184026331</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>20-07-2007</t>
+          <t>13-02-2010</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CARRILLOJAMILETH659@GMAIL.COM</t>
+          <t>EVERVZZESCOBEDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 08:07:32</t>
+          <t>09-02-2026 03:45:57</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 08:09:12</t>
+          <t>09-02-2026 03:48:37</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6550,7 +6550,7 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -6561,11 +6561,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26180522225160004069</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26180522173570003850</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>549</t>
@@ -6573,7 +6581,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Juan Alberto Hernandez Ruiz</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6585,12 +6593,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342704</t>
+          <t>342020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6600,17 +6608,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VERONICA ITZEL</t>
+          <t xml:space="preserve">CRISTIAN </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>RUEDA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE LA CRUZ </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6620,32 +6628,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8123545917</t>
+          <t>8132734280</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LIMANI 706</t>
+          <t>NICOLAS MICHELENA 1713</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>03-02-2002</t>
+          <t>27-11-1992</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FLORESVERONICA902@GMAIL.COM</t>
+          <t>RUEDACRISTIAN46@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10-02-2026 16:26:20</t>
+          <t>09-02-2026 07:05:35</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6666,17 +6674,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10-02-2026 16:33:21</t>
+          <t>09-02-2026 07:17:07</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10-02-2026 16:32:00</t>
+          <t>09-02-2026 07:14:13</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6696,7 +6704,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26180522236870004136</t>
+          <t>26180522182930003868</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6708,7 +6716,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6720,12 +6728,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342757</t>
+          <t>344285</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6735,17 +6743,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t xml:space="preserve">MARICRUZ </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CRISTERNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BETANCOURT</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6755,10 +6763,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8132784239</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>8110441305</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SANTA CATARINA</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6766,42 +6778,42 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08-02-2007</t>
+          <t>01-07-1997</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MARIAFERNANDACRISTERNABE@GMAIL.COM</t>
+          <t>MTZMARICRUZ31@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>10-02-2026 17:39:43</t>
+          <t>16-02-2026 18:27:29</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 18:47:33</t>
+          <t>16-02-2026 18:31:22</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6809,13 +6821,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>16-02-2026 18:30:30</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6823,22 +6843,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26180522405620004851</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522404740004848</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6855,12 +6867,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342201</t>
+          <t>342544</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6870,17 +6882,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>FATIMA JAMILETH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MEJIA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6890,28 +6902,28 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8121490904</t>
+          <t>8181377067</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>05-03-2009</t>
+          <t>20-07-2007</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ALEJANDRO.MTZDAVILA5@GMAIL.COM</t>
+          <t>CARRILLOJAMILETH659@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 15:01:11</t>
+          <t>10-02-2026 08:07:32</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6936,18 +6948,18 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:57</t>
+          <t>10-02-2026 08:09:12</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -6958,7 +6970,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26180522194600003915</t>
+          <t>26180522225160004069</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -6970,7 +6982,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6982,12 +6994,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342314</t>
+          <t>342704</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6997,17 +7009,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OZIEL RAUL </t>
+          <t>VERONICA ITZEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t xml:space="preserve">DE LA CRUZ </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7017,32 +7029,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8116392285</t>
+          <t>8123545917</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SAN GILBERTO</t>
+          <t>LIMANI 706</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>09-08-1989</t>
+          <t>03-02-2002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>OZIEL89@HOTMAIL.COM</t>
+          <t>FLORESVERONICA902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>09-02-2026 17:18:43</t>
+          <t>10-02-2026 16:26:20</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7063,17 +7075,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:44</t>
+          <t>10-02-2026 16:33:21</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:16</t>
+          <t>10-02-2026 16:32:00</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7093,7 +7105,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26180522201820003970</t>
+          <t>26180522236870004136</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7117,12 +7129,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>341614</t>
+          <t>342757</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7132,17 +7144,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>XIMENA ALEJANDRA</t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CRISTERNA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>BETANCOURT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7152,14 +7164,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6144578497</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>ASTORGA 322</t>
-        </is>
-      </c>
+          <t>8132784239</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7167,60 +7175,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15-06-2012</t>
+          <t>08-02-2007</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>XIMENATORRES150212@GMAIL.COM</t>
+          <t>MARIAFERNANDACRISTERNABE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>06-02-2026 16:02:10</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>10-02-2026 17:39:43</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10-02-2026 15:25:06</t>
+          <t>16-02-2026 18:47:33</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>10-02-2026 15:24:27</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7228,7 +7232,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26180522234410004112</t>
+          <t>26180522405620004851</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -7243,12 +7247,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7260,12 +7264,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>342201</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7275,17 +7279,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JARED MANASÉS</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERNÁNDEZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7295,7 +7299,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9511939543</t>
+          <t>8121490904</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7306,17 +7310,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>05-07-2005</t>
+          <t>05-03-2009</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MARCIALJARIS@GMAIL.COM</t>
+          <t>ALEJANDRO.MTZDAVILA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>07-02-2026 21:58:54</t>
+          <t>09-02-2026 15:01:11</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7341,12 +7345,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>09-02-2026 18:25:04</t>
+          <t>09-02-2026 15:05:57</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -7363,14 +7367,10 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26180522207000003988</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522194600003915</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
@@ -7379,24 +7379,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344285</t>
+          <t>342314</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7406,17 +7406,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARICRUZ </t>
+          <t xml:space="preserve">OZIEL RAUL </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7426,39 +7426,35 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8110441305</t>
+          <t>8116392285</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SANTA CATARINA</t>
+          <t>SAN GILBERTO</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01-07-1997</t>
+          <t>09-08-1989</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MTZMARICRUZ31@GMAIL.COM</t>
+          <t>OZIEL89@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 18:27:29</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:18:43</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7476,17 +7472,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-02-2026 18:31:22</t>
+          <t>09-02-2026 17:21:44</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>16-02-2026 18:30:30</t>
+          <t>09-02-2026 17:21:16</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7506,7 +7502,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26180522404740004848</t>
+          <t>26180522201820003970</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7518,7 +7514,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7530,12 +7526,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>341984</t>
+          <t>341614</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7545,17 +7541,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EVER ALBERTO</t>
+          <t>XIMENA ALEJANDRA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ESCOBEDO</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7565,53 +7561,53 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8184026331</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6144578497</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ASTORGA 322</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>13-02-2010</t>
+          <t>15-06-2012</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>EVERVZZESCOBEDO@GMAIL.COM</t>
+          <t>XIMENATORRES150212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>09-02-2026 03:45:57</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 16:02:10</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>09-02-2026 03:48:37</t>
+          <t>10-02-2026 15:25:06</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -7619,13 +7615,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:24:27</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7633,7 +7637,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26180522173570003850</t>
+          <t>26180522234410004112</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7643,17 +7647,17 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>LILIANA SARAHI MORALES VARGAS</t>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Juan Alberto Hernandez Ruiz</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7665,12 +7669,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342020</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7680,17 +7684,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN </t>
+          <t>JARED MANASÉS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RUEDA</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>HERNÁNDEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7700,14 +7704,10 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8132734280</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>NICOLAS MICHELENA 1713</t>
-        </is>
-      </c>
+          <t>9511939543</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7715,60 +7715,56 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>27-11-1992</t>
+          <t>05-07-2005</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RUEDACRISTIAN46@GMAIL.COM</t>
+          <t>MARCIALJARIS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>09-02-2026 07:05:35</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>07-02-2026 21:58:54</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>09-02-2026 07:17:07</t>
+          <t>09-02-2026 18:25:04</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>09-02-2026 07:14:13</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7776,36 +7772,40 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26180522182930003868</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
+          <t>26180522207000003988</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342168</t>
+          <t>342242</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7815,17 +7815,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KEVIN MIGUEL</t>
+          <t>EVA MARIANA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ALFARO</t>
+          <t>MAYA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7835,32 +7835,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8126005764</t>
+          <t>8134495854</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BOSQUE DE ABEDULES 642</t>
+          <t>METROPLEX</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>30-09-2002</t>
+          <t>17-03-1998</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>KEVINMIGUELALFARODIAZ2002@GMAIL.COM</t>
+          <t>MARIANAMAYARDZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>09-02-2026 13:57:17</t>
+          <t>09-02-2026 16:10:28</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>09-02-2026 14:12:38</t>
+          <t>09-02-2026 16:23:15</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>09-02-2026 14:11:08</t>
+          <t>09-02-2026 16:22:54</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26180522192670003905</t>
+          <t>26180522197900003949</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Aurora Nohemi Juarez Garza</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7939,12 +7939,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342242</t>
+          <t>342168</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7954,17 +7954,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EVA MARIANA</t>
+          <t>KEVIN MIGUEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MAYA</t>
+          <t>ALFARO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7974,32 +7974,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8134495854</t>
+          <t>8126005764</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>METROPLEX</t>
+          <t>BOSQUE DE ABEDULES 642</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>17-03-1998</t>
+          <t>30-09-2002</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>MARIANAMAYARDZ@GMAIL.COM</t>
+          <t>KEVINMIGUELALFARODIAZ2002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>09-02-2026 16:10:28</t>
+          <t>09-02-2026 13:57:17</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>09-02-2026 16:23:15</t>
+          <t>09-02-2026 14:12:38</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>09-02-2026 16:22:54</t>
+          <t>09-02-2026 14:11:08</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26180522197900003949</t>
+          <t>26180522192670003905</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Aurora Nohemi Juarez Garza</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8078,12 +8078,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>345086</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HANNA MARIVI</t>
+          <t>JHONJAIRO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8113,35 +8113,39 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8135670542</t>
+          <t>8112289625</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">JARDINES </t>
+          <t>TOBOSOS 101</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>02-04-2002</t>
+          <t>16-02-2006</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>HANNASALAZAR.240419@GMAIL.COM</t>
+          <t>JHONJAIRODIAZ61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>12-02-2026 16:40:10</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>19-02-2026 15:00:58</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8154,22 +8158,22 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>17-02-2026 08:00:00</t>
+          <t>19-02-2026 15:05:11</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>16-02-2026 16:30:42</t>
+          <t>19-02-2026 15:04:37</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8189,22 +8193,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26180522419670004906</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522496050005244</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
@@ -8221,12 +8217,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>345086</t>
+          <t>343317</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>87251</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8236,17 +8232,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JHONJAIRO</t>
+          <t>HANNA MARIVI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8256,39 +8252,35 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8112289625</t>
+          <t>8135670542</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TOBOSOS 101</t>
+          <t xml:space="preserve">JARDINES </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16-02-2006</t>
+          <t>02-04-2002</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>JHONJAIRODIAZ61@GMAIL.COM</t>
+          <t>HANNASALAZAR.240419@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19-02-2026 15:00:58</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 16:40:10</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8301,22 +8293,22 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>19-02-2026 15:05:11</t>
+          <t>17-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>19-02-2026 15:04:37</t>
+          <t>16-02-2026 16:30:42</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8336,14 +8328,22 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26180522496050005244</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26180522419670004906</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8642,12 +8642,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>342806</t>
+          <t>346561</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>88726</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8657,17 +8657,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MANUEL ALBERTO</t>
+          <t>EDDY DANIEL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CURIQUEO</t>
+          <t>GUERRA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8677,10 +8677,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8126387214</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>8127330165</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>JUAN SLAZAR 1835</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8688,17 +8692,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31-01-1995</t>
+          <t>02-03-1995</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>MANUCCQUEO@GMAIL.COM</t>
+          <t>EWAR0302@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>10-02-2026 18:38:14</t>
+          <t>25-02-2026 18:13:17</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8708,36 +8712,44 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>10-02-2026 18:40:47</t>
+          <t>25-02-2026 18:17:14</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:16:32</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8745,19 +8757,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26180522244290004176</t>
+          <t>26180522662920005921</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8769,12 +8781,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>346561</t>
+          <t>346784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>88726</t>
+          <t>88949</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8784,17 +8796,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EDDY DANIEL</t>
+          <t>DIEGO LAURO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GUERRA</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>LEOS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8804,14 +8816,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8127330165</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>JUAN SLAZAR 1835</t>
-        </is>
-      </c>
+          <t>8123606684</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8819,64 +8827,56 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>02-03-1995</t>
+          <t>24-04-2009</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>EWAR0302@GMAIL.COM</t>
+          <t>DEADPOOL80P3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>25-02-2026 18:13:17</t>
+          <t>26-02-2026 17:43:36</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>25-02-2026 18:17:14</t>
+          <t>26-02-2026 17:44:44</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>25-02-2026 18:16:32</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8884,14 +8884,14 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26180522662920005921</t>
+          <t>26180522690470006056</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8908,12 +8908,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344065</t>
+          <t>342806</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8923,17 +8923,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>JESSICA ELIZABETH</t>
+          <t>MANUEL ALBERTO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CURIQUEO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8943,79 +8943,67 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8117232420</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>RIO ATOYA</t>
-        </is>
-      </c>
+          <t>8126387214</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>23-12-1991</t>
+          <t>31-01-1995</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>AROMELY_23@OUTLOOK.COM</t>
+          <t>MANUCCQUEO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 13:19:23</t>
+          <t>10-02-2026 18:38:14</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 13:24:31</t>
+          <t>10-02-2026 18:40:47</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>16-02-2026 13:23:46</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9023,19 +9011,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26180522388570004746</t>
+          <t>26180522244290004176</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9047,12 +9035,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>346784</t>
+          <t>343464</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>88949</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9062,17 +9050,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DIEGO LAURO</t>
+          <t>FRANCISCO ALEJANDRO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LEOS</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9082,10 +9070,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8123606684</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>8130448891</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TEODORO LANDAURO 1000</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -9093,56 +9085,60 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>24-04-2009</t>
+          <t>17-05-1999</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>DEADPOOL80P3@GMAIL.COM</t>
+          <t>AC811246@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>26-02-2026 17:43:36</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>13-02-2026 10:30:04</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>26-02-2026 17:44:44</t>
+          <t>13-02-2026 10:37:33</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>13-02-2026 10:36:45</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9150,14 +9146,14 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26180522690470006056</t>
+          <t>26180522318330004518</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9853,12 +9849,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>343464</t>
+          <t>344065</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9868,17 +9864,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FRANCISCO ALEJANDRO</t>
+          <t>JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9888,35 +9884,39 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8130448891</t>
+          <t>8117232420</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TEODORO LANDAURO 1000</t>
+          <t>RIO ATOYA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17-05-1999</t>
+          <t>23-12-1991</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>AC811246@GMAIL.COM</t>
+          <t>AROMELY_23@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>13-02-2026 10:30:04</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>16-02-2026 13:19:23</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9934,17 +9934,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>13-02-2026 10:37:33</t>
+          <t>16-02-2026 13:24:31</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13-02-2026 10:36:45</t>
+          <t>16-02-2026 13:23:46</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26180522318330004518</t>
+          <t>26180522388570004746</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10270,12 +10270,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>345088</t>
+          <t>344876</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>87253</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO </t>
+          <t>GUSTAVO ANDRES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>RINCON</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MARFIL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8119638301</t>
+          <t>8117369832</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>HACIENDA DEL FRESNO 110</t>
+          <t>CALLE 1 409</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10320,52 +10320,52 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>30-09-2006</t>
+          <t>28-08-1981</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>RICARDO.ROJAS9920@ICLOUD.COM</t>
+          <t>GRINCON@BOMBEROSDENUEVOLEON.RG</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>19-02-2026 15:09:00</t>
+          <t>18-02-2026 16:48:08</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>19-02-2026 15:13:05</t>
+          <t>18-02-2026 17:13:33</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>19-02-2026 15:12:37</t>
+          <t>18-02-2026 17:13:05</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10385,14 +10385,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26180522496250005246</t>
+          <t>26180522468530005143</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10409,12 +10409,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>344176</t>
+          <t>344652</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10424,17 +10424,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MARIO CESAR</t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">MOLINA </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LUCIO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10444,32 +10444,28 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8125930595</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>VIÑEDO ITALIANO</t>
-        </is>
-      </c>
+          <t>8180873008</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>25-09-2001</t>
+          <t>18-01-2007</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>GAZERSERENITY@GMAIL.COM</t>
+          <t>YAMGARC007@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>16-02-2026 16:46:48</t>
+          <t>17-02-2026 18:16:42</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10479,44 +10475,36 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>16-02-2026 17:14:56</t>
+          <t>17-02-2026 18:19:15</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:14:29</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10524,14 +10512,14 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26180522398330004810</t>
+          <t>26180522441000005015</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10548,12 +10536,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>344652</t>
+          <t>344176</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10563,17 +10551,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t>MARIO CESAR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINA </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LUCIO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10583,28 +10571,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8180873008</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>8125930595</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>VIÑEDO ITALIANO</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>18-01-2007</t>
+          <t>25-09-2001</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>YAMGARC007@GMAIL.COM</t>
+          <t>GAZERSERENITY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>17-02-2026 18:16:42</t>
+          <t>16-02-2026 16:46:48</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10614,36 +10606,44 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>17-02-2026 18:19:15</t>
+          <t>16-02-2026 17:14:56</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:14:29</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10651,14 +10651,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26180522441000005015</t>
+          <t>26180522398330004810</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10675,12 +10675,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>344876</t>
+          <t>344881</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10690,17 +10690,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GUSTAVO ANDRES</t>
+          <t>DANTE GERARDO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RINCON</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MARFIL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10710,14 +10710,10 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8117369832</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>CALLE 1 409</t>
-        </is>
-      </c>
+          <t>8124376476</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10725,17 +10721,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>28-08-1981</t>
+          <t>24-07-2010</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>GRINCON@BOMBEROSDENUEVOLEON.RG</t>
+          <t>DANTEAVILAG24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>18-02-2026 16:48:08</t>
+          <t>18-02-2026 17:03:35</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10745,22 +10741,22 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>18-02-2026 17:13:33</t>
+          <t>18-02-2026 17:05:09</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10768,21 +10764,13 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>18-02-2026 17:13:05</t>
-        </is>
-      </c>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10790,14 +10778,14 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26180522468530005143</t>
+          <t>26180522468080005136</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -10814,12 +10802,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>344473</t>
+          <t>345088</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10829,17 +10817,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t xml:space="preserve">RICARDO </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10849,10 +10837,14 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8119077656</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>8119638301</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>HACIENDA DEL FRESNO 110</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10860,56 +10852,64 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>04-02-2008</t>
+          <t>30-09-2006</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>RODRIGO.INSTAPIC@GMAIL.COM</t>
+          <t>RICARDO.ROJAS9920@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>17-02-2026 13:03:56</t>
+          <t>19-02-2026 15:09:00</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>17-02-2026 13:04:47</t>
+          <t>19-02-2026 15:13:05</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:12:37</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10917,14 +10917,14 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26180522427280004929</t>
+          <t>26180522496250005246</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10941,12 +10941,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>344575</t>
+          <t>344473</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10956,17 +10956,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -10976,28 +10976,28 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8154541233</t>
+          <t>8119077656</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>30-10-1983</t>
+          <t>04-02-2008</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>GABB301083@GMAIL.COM</t>
+          <t>RODRIGO.INSTAPIC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:43:36</t>
+          <t>17-02-2026 13:03:56</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11012,17 +11012,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>17-02-2026 16:45:26</t>
+          <t>17-02-2026 13:04:47</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -11033,7 +11033,7 @@
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V79" t="inlineStr"/>
@@ -11044,14 +11044,14 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26180522435020004990</t>
+          <t>26180522427280004929</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -11068,12 +11068,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>344101</t>
+          <t>344575</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11083,17 +11083,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PATRICIO</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -11103,32 +11103,28 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8186800359</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>CALLE ALTOCUMULUS 310</t>
-        </is>
-      </c>
+          <t>8154541233</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>16-08-2003</t>
+          <t>30-10-1983</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>PATRICIOHDZ2009@HOTMAIL.COM</t>
+          <t>GABB301083@GMAIL.COM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>16-02-2026 14:43:09</t>
+          <t>17-02-2026 16:43:36</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -11138,44 +11134,36 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>19-02-2026 15:15:54</t>
+          <t>17-02-2026 16:45:26</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>19-02-2026 15:15:11</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11183,18 +11171,14 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>26180522496340005247</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522435020004990</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11211,12 +11195,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>344881</t>
+          <t>345118</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11226,17 +11210,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DANTE GERARDO</t>
+          <t>HECTOR MAURICIO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GARIBAY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -11246,28 +11230,28 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8124376476</t>
+          <t>8181810051</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>24-07-2010</t>
+          <t>14-01-1997</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>DANTEAVILAG24@GMAIL.COM</t>
+          <t>MAURICIO.MTZG@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>18-02-2026 17:03:35</t>
+          <t>19-02-2026 16:07:08</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11282,28 +11266,28 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>18-02-2026 17:05:09</t>
+          <t>19-02-2026 16:08:57</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V81" t="inlineStr"/>
@@ -11314,14 +11298,14 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>26180522468080005136</t>
+          <t>26180522498220005267</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -11338,12 +11322,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>345937</t>
+          <t>345344</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>88102</t>
+          <t>87509</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11353,17 +11337,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ADELFA GABRIELA</t>
+          <t>CRISTIAN OSWALDO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -11373,67 +11357,67 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8120265470</t>
+          <t>8128805087</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SIERRA DEL ESPINAZO 1113</t>
+          <t>PALMA CHICA 831</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>10-03-2004</t>
+          <t>01-05-1993</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>GF961430@GMAIL.COM</t>
+          <t>CRISTIANOSWALDOFELIXZUNIGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>23-02-2026 17:44:31</t>
+          <t>20-02-2026 16:56:25</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>23-02-2026 17:49:59</t>
+          <t>25-02-2026 16:18:00</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>23-02-2026 17:49:01</t>
+          <t>25-02-2026 16:17:21</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -11443,7 +11427,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -11453,36 +11437,44 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>26180522592650005629</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
+          <t>26180522657120005893</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>344880</t>
+          <t>344101</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11492,17 +11484,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>PATRICIO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ROGEL</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11512,28 +11504,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8129128953</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>8186800359</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>CALLE ALTOCUMULUS 310</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>16-08-2003</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>VALERIAROGELHDZ@GMAIL.COM</t>
+          <t>PATRICIOHDZ2009@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>18-02-2026 16:58:52</t>
+          <t>16-02-2026 14:43:09</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11543,36 +11539,44 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>18-02-2026 17:00:33</t>
+          <t>19-02-2026 15:15:54</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:15:11</t>
+        </is>
+      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W83" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11580,14 +11584,18 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26180522467780005133</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr"/>
+          <t>26180522496340005247</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -11604,12 +11612,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>345118</t>
+          <t>344880</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>87283</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11619,17 +11627,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HECTOR MAURICIO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ROGEL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GARIBAY</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -11639,7 +11647,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8181810051</t>
+          <t>8129128953</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11650,17 +11658,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>14-01-1997</t>
+          <t>21-11-2007</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>MAURICIO.MTZG@HOTMAIL.COM</t>
+          <t>VALERIAROGELHDZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>19-02-2026 16:07:08</t>
+          <t>18-02-2026 16:58:52</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11675,22 +11683,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>19-02-2026 16:08:57</t>
+          <t>18-02-2026 17:00:33</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -11707,14 +11715,14 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26180522498220005267</t>
+          <t>26180522467780005133</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -11731,12 +11739,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>345344</t>
+          <t>345937</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>88102</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11746,17 +11754,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CRISTIAN OSWALDO</t>
+          <t>ADELFA GABRIELA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11766,67 +11774,67 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8128805087</t>
+          <t>8120265470</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>PALMA CHICA 831</t>
+          <t>SIERRA DEL ESPINAZO 1113</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>01-05-1993</t>
+          <t>10-03-2004</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CRISTIANOSWALDOFELIXZUNIGA@GMAIL.COM</t>
+          <t>GF961430@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>20-02-2026 16:56:25</t>
+          <t>23-02-2026 17:44:31</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>25-02-2026 16:18:00</t>
+          <t>23-02-2026 17:49:59</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>25-02-2026 16:17:21</t>
+          <t>23-02-2026 17:49:01</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -11836,7 +11844,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -11846,44 +11854,36 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26180522657120005893</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522592650005629</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>346689</t>
+          <t>345302</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>88854</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11893,17 +11893,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LUIS DAVID</t>
+          <t xml:space="preserve">FRACISCO JAVIER </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MORIN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -11913,14 +11913,10 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8135356066</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>VALLADOLID 3014</t>
-        </is>
-      </c>
+          <t>8114668597</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -11928,64 +11924,52 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>10-04-2004</t>
+          <t>01-10-2003</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>LCERDAS1840@HOTMAIL.COM</t>
+          <t>FRANCISTOTI88@GMAIL.COM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>26-02-2026 12:00:01</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>20-02-2026 15:17:35</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>26-02-2026 12:02:26</t>
+          <t>20-02-2026 15:20:10</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>26-02-2026 12:02:06</t>
-        </is>
-      </c>
+          <t>20-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11993,19 +11977,19 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>26180522681140005981</t>
+          <t>26180522528270005374</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12017,12 +12001,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>345302</t>
+          <t>346139</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>87467</t>
+          <t>88304</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12032,17 +12016,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACISCO JAVIER </t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MORIN</t>
+          <t>CEPEDA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -12052,10 +12036,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8114668597</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>8110726899</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>PUNTA NORTE 147</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -12063,52 +12051,64 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01-10-2003</t>
+          <t>19-05-1987</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>FRANCISTOTI88@GMAIL.COM</t>
+          <t>GERARDOGARZACEPEDA19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>20-02-2026 15:17:35</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>24-02-2026 12:28:42</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>20-02-2026 15:20:10</t>
+          <t>27-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>20-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>27-02-2026 08:16:13</t>
+        </is>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12116,36 +12116,40 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26180522528270005374</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr"/>
+          <t>26180522706380006106</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>346139</t>
+          <t>346689</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>88854</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12155,17 +12159,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>LUIS DAVID</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CEPEDA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12175,12 +12179,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8110726899</t>
+          <t>8135356066</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>PUNTA NORTE 147</t>
+          <t>VALLADOLID 3014</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -12190,17 +12194,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>19-05-1987</t>
+          <t>10-04-2004</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>GERARDOGARZACEPEDA19@GMAIL.COM</t>
+          <t>LCERDAS1840@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>24-02-2026 12:28:42</t>
+          <t>26-02-2026 12:00:01</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -12225,17 +12229,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>27-02-2026 08:16:52</t>
+          <t>26-02-2026 12:02:26</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>27-02-2026 08:16:13</t>
+          <t>26-02-2026 12:02:06</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -12245,7 +12249,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -12255,14 +12259,10 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26180522706380006106</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522681140005981</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
@@ -12271,12 +12271,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347413</t>
+          <t>347341</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89578</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CLAUDIA ELENA</t>
+          <t>MILTON ALONSO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SEPULVEDA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>BOCANEGRA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,35 +613,31 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8112123898</t>
+          <t>8136817474</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24-11-1969</t>
+          <t>20-04-2009</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SAVY90@HOTMAIL.COM</t>
+          <t>MILTONALO200478@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:12:03</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-03-2026 12:36:53</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -649,22 +645,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:14:01</t>
+          <t>01-03-2026 12:38:51</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,14 +677,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26180522781780006313</t>
+          <t>26180522769180006280</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -705,12 +701,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347341</t>
+          <t>301839</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>99337</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +716,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MILTON ALONSO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BOCANEGRA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,10 +736,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8136817474</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>8119155852</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ANTONIO MACHADO 2953</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -751,52 +751,60 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-04-2009</t>
+          <t>02-09-1993</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MILTONALO200478@GMAIL.COM</t>
+          <t>CERDAJAIME75@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:53</t>
+          <t>02-07-2025 19:04:12</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 12:38:51</t>
+          <t>02-03-2026 17:16:38</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:15:49</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -804,24 +812,28 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180522769180006280</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26180522805690006432</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -955,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301839</t>
+          <t>346395</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99337</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -970,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>DAVID ALBERTO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -990,12 +1002,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8119155852</t>
+          <t>8122174357</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ANTONIO MACHADO 2953</t>
+          <t>EPIGMENIO GONZALEZ 1626</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1005,17 +1017,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-09-1993</t>
+          <t>12-12-1994</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CERDAJAIME75@GMAIL.COM</t>
+          <t>GALVANALBERTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-07-2025 19:04:12</t>
+          <t>25-02-2026 08:58:03</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1036,7 +1048,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:38</t>
+          <t>02-03-2026 07:16:28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1046,7 +1058,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 17:15:49</t>
+          <t>02-03-2026 07:14:40</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1056,7 +1068,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1066,12 +1078,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522805690006432</t>
+          <t>26180522781930006316</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1094,12 +1106,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346395</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,17 +1121,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAVID ALBERTO</t>
+          <t>CLAUDIA ELENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SEPULVEDA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1129,75 +1141,67 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8122174357</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>EPIGMENIO GONZALEZ 1626</t>
-        </is>
-      </c>
+          <t>8112123898</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>12-12-1994</t>
+          <t>24-11-1969</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GALVANALBERTO1994@GMAIL.COM</t>
+          <t>SAVY90@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25-02-2026 08:58:03</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>02-03-2026 07:12:03</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:28</t>
+          <t>02-03-2026 07:14:01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:14:40</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1205,18 +1209,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522781930006316</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522781780006313</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1233,12 +1233,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>347973</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>90138</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>ISABEL DEL CARMEN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>QUIXTIANO</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2381803817</t>
+          <t>8127472290</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VIÑEDO ARGENTINO 313</t>
+          <t>RIO TAMAZUNCHALE 770</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1283,52 +1283,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
+          <t>SEGURAGISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:32:17</t>
+          <t>03-03-2026 08:47:11</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:38:45</t>
+          <t>03-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:29</t>
+          <t>03-03-2026 08:49:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1348,14 +1348,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26180522807300006437</t>
+          <t>26180522833940006519</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ELIJIO</t>
+          <t xml:space="preserve">PINEDA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,67 +1407,79 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8116124131</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>8135334064</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CERRO DE LA MITRAS 2855</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-01-1995</t>
+          <t>18-09-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PATTY_ALE22@HOTMAIL.COM</t>
+          <t>GABRIELPINEDA338@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:16:39</t>
+          <t>25-02-2026 15:27:11</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:17:52</t>
+          <t>03-03-2026 19:32:56</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:47</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1475,14 +1487,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26180522801020006411</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26180522859170006657</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1499,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1514,12 +1534,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL OSMAR </t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>QUIXTIANO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1534,53 +1554,57 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8136248116</t>
+          <t>2381803817</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ANTONIO MACHADO</t>
+          <t>VIÑEDO ARGENTINO 313</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ANGEL.OSMAR13@GMAIL.COM</t>
+          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:17</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>02-03-2026 17:32:17</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:56</t>
+          <t>02-03-2026 17:38:45</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1590,7 +1614,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:32</t>
+          <t>02-03-2026 17:37:29</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1600,7 +1624,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1610,22 +1634,1098 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522806130006433</t>
+          <t>26180522807300006437</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347361</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89526</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MARIA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RETTA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8331812722</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FRESNO 210</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>23-05-1992</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CONNIRETTA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>01-03-2026 18:40:28</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 04:12:23</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 04:11:38</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26180522822020006489</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348242</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90407</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MELISSA YOSELIN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8132524700</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DE LA ESCULTURA 1102</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11-08-1999</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:46:27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:51:58</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26180522856500006642</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347669</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>89834</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ELIJIO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8116124131</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>22-01-1995</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PATTY_ALE22@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:16:39</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:17:52</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26180522801020006411</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347731</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>89896</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL OSMAR </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CERDA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8136248116</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ANTONIO MACHADO</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>29-01-2000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ANGEL.OSMAR13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:21:56</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:21:32</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26180522806130006433</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347945</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90110</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MAURICIO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8133810118</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03-05-2010</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:17:52</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:19:03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26180522831500006511</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348053</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90218</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JOSE ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MELENDEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8136064783</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN MIGUEL 104</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10-06-1994</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:44:27</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:54:18</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:53:48</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26180522840700006538</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348115</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90280</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MELANY AMINADAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AMARO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ONTIVEROS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8134091393</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>15-02-2007</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:20:18</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:23:04</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26180522846460006583</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348239</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90404</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ANGELA VERONICA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8113984035</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C DE LA PINTURA 1100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05-12-2004</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AVIG051204@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:43:11</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:49:27</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:48:23</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26180522856360006639</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347341</t>
+          <t>301839</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>99337</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MILTON ALONSO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BOCANEGRA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8136817474</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>8119155852</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ANTONIO MACHADO 2953</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -624,52 +628,60 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-04-2009</t>
+          <t>02-09-1993</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MILTONALO200478@GMAIL.COM</t>
+          <t>CERDAJAIME75@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:53</t>
+          <t>02-07-2025 19:04:12</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 12:38:51</t>
+          <t>02-03-2026 17:16:38</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:15:49</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -677,36 +689,40 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26180522769180006280</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26180522805690006432</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301839</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99337</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t xml:space="preserve">PINEDA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -736,12 +752,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8119155852</t>
+          <t>8135334064</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ANTONIO MACHADO 2953</t>
+          <t>CERRO DE LA MITRAS 2855</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -751,20 +767,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-09-1993</t>
+          <t>18-09-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CERDAJAIME75@GMAIL.COM</t>
+          <t>GABRIELPINEDA338@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-07-2025 19:04:12</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>25-02-2026 15:27:11</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -772,27 +792,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:38</t>
+          <t>03-03-2026 19:32:56</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:15:49</t>
+          <t>03-03-2026 19:31:47</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -812,28 +832,32 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180522805690006432</t>
+          <t>26180522859170006657</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -967,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346395</t>
+          <t>347341</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -982,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DAVID ALBERTO</t>
+          <t>MILTON ALONSO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>BOCANEGRA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1002,14 +1026,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8122174357</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>EPIGMENIO GONZALEZ 1626</t>
-        </is>
-      </c>
+          <t>8136817474</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1017,60 +1037,52 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-12-1994</t>
+          <t>20-04-2009</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>GALVANALBERTO1994@GMAIL.COM</t>
+          <t>MILTONALO200478@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25-02-2026 08:58:03</t>
+          <t>01-03-2026 12:36:53</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:28</t>
+          <t>01-03-2026 12:38:51</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:14:40</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1078,18 +1090,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522781930006316</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522769180006280</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1106,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347413</t>
+          <t>346395</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89578</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLAUDIA ELENA</t>
+          <t>DAVID ALBERTO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEPULVEDA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1141,67 +1149,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8112123898</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>8122174357</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EPIGMENIO GONZALEZ 1626</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-11-1969</t>
+          <t>12-12-1994</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SAVY90@HOTMAIL.COM</t>
+          <t>GALVANALBERTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:12:03</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:58:03</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:14:01</t>
+          <t>02-03-2026 07:16:28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:14:40</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1209,14 +1225,18 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522781780006313</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26180522781930006316</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1233,12 +1253,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347973</t>
+          <t>347361</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90138</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1248,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ISABEL DEL CARMEN</t>
+          <t>MARIA CONCEPCION</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RETTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1268,12 +1288,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8127472290</t>
+          <t>8331812722</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RIO TAMAZUNCHALE 770</t>
+          <t>FRESNO 210</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1283,42 +1303,42 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-02-1998</t>
+          <t>23-05-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SEGURAGISA@GMAIL.COM</t>
+          <t>CONNIRETTA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:11</t>
+          <t>01-03-2026 18:40:28</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:14</t>
+          <t>03-03-2026 04:12:23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1328,7 +1348,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 08:49:30</t>
+          <t>03-03-2026 04:11:38</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1348,14 +1368,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26180522833940006519</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26180522822020006489</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1372,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346506</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PINEDA </t>
+          <t>QUIXTIANO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,67 +1431,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8135334064</t>
+          <t>2381803817</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CERRO DE LA MITRAS 2855</t>
+          <t>VIÑEDO ARGENTINO 313</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18-09-2004</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GABRIELPINEDA338@GMAIL.COM</t>
+          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25-02-2026 15:27:11</t>
+          <t>02-03-2026 17:32:17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:56</t>
+          <t>02-03-2026 17:38:45</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 19:31:47</t>
+          <t>02-03-2026 17:37:29</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1477,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1487,22 +1511,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26180522859170006657</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522807300006437</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1519,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>347362</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t xml:space="preserve">ALED </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QUIXTIANO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,79 +1570,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2381803817</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>VIÑEDO ARGENTINO 313</t>
-        </is>
-      </c>
+          <t>8180518618</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>15-02-2012</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
+          <t>ALEESGN92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:32:17</t>
+          <t>01-03-2026 21:21:25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:38:45</t>
+          <t>04-03-2026 15:50:40</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:37:29</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1634,36 +1638,40 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522807300006437</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26180522885900006745</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347361</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA CONCEPCION</t>
+          <t>CLAUDIA ELENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>SEPULVEDA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RETTA</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,14 +1701,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8331812722</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FRESNO 210</t>
-        </is>
-      </c>
+          <t>8112123898</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1708,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23-05-1992</t>
+          <t>24-11-1969</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CONNIRETTA@GMAIL.COM</t>
+          <t>SAVY90@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 18:40:28</t>
+          <t>02-03-2026 07:12:03</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1728,44 +1732,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 04:12:23</t>
+          <t>02-03-2026 07:14:01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>03-03-2026 04:11:38</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1773,18 +1769,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26180522822020006489</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522781780006313</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1801,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348242</t>
+          <t>347648</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1816,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MELISSA YOSELIN</t>
+          <t>MIA YOSELIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1836,14 +1828,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8132524700</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DE LA ESCULTURA 1102</t>
-        </is>
-      </c>
+          <t>8188055318</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1851,32 +1839,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11-08-1999</t>
+          <t>30-09-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+          <t>MREY4604@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 18:46:27</t>
+          <t>02-03-2026 15:49:35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1886,29 +1874,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:58</t>
+          <t>05-03-2026 16:03:29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:51:15</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1916,10 +1896,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26180522856500006642</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26180522920130006900</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -2067,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>347945</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>90110</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2082,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL OSMAR </t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2102,14 +2086,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8136248116</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ANTONIO MACHADO</t>
-        </is>
-      </c>
+          <t>8133810118</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2117,60 +2097,56 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>03-05-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ANGEL.OSMAR13@GMAIL.COM</t>
+          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:17</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>03-03-2026 07:17:52</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:56</t>
+          <t>03-03-2026 07:19:03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:21:32</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2178,14 +2154,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26180522806130006433</t>
+          <t>26180522831500006511</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2202,12 +2178,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347945</t>
+          <t>348053</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90110</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2217,17 +2193,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2237,10 +2213,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8133810118</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>8136064783</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN MIGUEL 104</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2248,32 +2228,32 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-05-2010</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
+          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 07:17:52</t>
+          <t>03-03-2026 13:44:27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2283,7 +2263,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 07:19:03</t>
+          <t>03-03-2026 13:54:18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2291,13 +2271,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:53:48</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2305,7 +2293,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26180522831500006511</t>
+          <t>26180522840700006538</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2329,12 +2317,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348053</t>
+          <t>348115</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2344,17 +2332,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>MELANY AMINADAY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>AMARO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2364,47 +2352,43 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8136064783</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>HACIENDA SAN MIGUEL 104</t>
-        </is>
-      </c>
+          <t>8134091393</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>15-02-2007</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
+          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 13:44:27</t>
+          <t>03-03-2026 16:20:18</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2414,7 +2398,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 13:54:18</t>
+          <t>03-03-2026 16:23:04</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2422,21 +2406,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>03-03-2026 13:53:48</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2444,7 +2420,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26180522840700006538</t>
+          <t>26180522846460006583</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2468,12 +2444,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348115</t>
+          <t>347731</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90280</t>
+          <t>89896</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2483,17 +2459,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MELANY AMINADAY</t>
+          <t xml:space="preserve">ANGEL OSMAR </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AMARO</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2503,67 +2479,75 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8134091393</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>8136248116</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ANTONIO MACHADO</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-02-2007</t>
+          <t>29-01-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
+          <t>ANGEL.OSMAR13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:18</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>02-03-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 16:23:04</t>
+          <t>02-03-2026 17:21:56</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:21:32</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2571,14 +2555,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26180522846460006583</t>
+          <t>26180522806130006433</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2595,12 +2579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>347973</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90138</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2610,17 +2594,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ANGELA VERONICA</t>
+          <t>ISABEL DEL CARMEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2630,12 +2614,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8113984035</t>
+          <t>8127472290</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C DE LA PINTURA 1100</t>
+          <t>RIO TAMAZUNCHALE 770</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2645,17 +2629,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>AVIG051204@GMAIL.COM</t>
+          <t>SEGURAGISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:11</t>
+          <t>03-03-2026 08:47:11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2680,7 +2664,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:27</t>
+          <t>03-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2690,7 +2674,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-03-2026 18:48:23</t>
+          <t>03-03-2026 08:49:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2700,7 +2684,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2710,7 +2694,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522856360006639</t>
+          <t>26180522833940006519</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2726,6 +2710,808 @@
         </is>
       </c>
       <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348239</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90404</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ANGELA VERONICA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8113984035</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C DE LA PINTURA 1100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>05-12-2004</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AVIG051204@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:43:11</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:49:27</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:48:23</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26180522856360006639</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348452</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90617</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN PABLO </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>URBINA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8123469708</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05-10-2009</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JURBINARODRIGU@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:04:34</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:05:47</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26180522884370006734</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348674</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90839</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8148715957</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>05-09-2003</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CG028887@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:04:41</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:05:48</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26180522914190006861</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348762</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90927</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CYNTHIA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CORTES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MONTIEL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8121933568</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PASEO DEL MILAGRO 1027</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>31-03-2007</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:07:33</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:22:45</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:20:29</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26180522923710006941</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348242</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90407</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MELISSA YOSELIN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8132524700</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>DE LA ESCULTURA 1102</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>11-08-1999</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:46:27</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:51:58</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26180522856500006642</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348480</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90645</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>INGRID</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ARIAS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CEDILLO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8116811694</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>18-09-2007</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>INGRIDARIAS509@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:22:02</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:24:31</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26180522887130006762</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346506</t>
+          <t>347362</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t xml:space="preserve">ALED </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PINEDA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,14 +752,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8135334064</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CERRO DE LA MITRAS 2855</t>
-        </is>
-      </c>
+          <t>8180518618</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -767,32 +763,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18-09-2004</t>
+          <t>15-02-2012</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GABRIELPINEDA338@GMAIL.COM</t>
+          <t>ALEESGN92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-02-2026 15:27:11</t>
+          <t>01-03-2026 21:21:25</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -802,7 +798,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:56</t>
+          <t>04-03-2026 15:50:40</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -810,21 +806,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:31:47</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -832,19 +820,15 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180522859170006657</t>
+          <t>26180522885900006745</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -852,24 +836,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347415</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89580</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JUAN DE DIOS</t>
+          <t>CLAUDIA ELENA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CHAGOLLAN</t>
+          <t>SEPULVEDA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OLAVARRIETA</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,33 +883,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8186811600</t>
+          <t>8112123898</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-08-1983</t>
+          <t>24-11-1969</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JC_F11@HOTMAIL.COM</t>
+          <t>SAVY90@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:38</t>
+          <t>02-03-2026 07:12:03</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -935,22 +919,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:17:45</t>
+          <t>02-03-2026 07:14:01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -967,14 +951,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26180522781970006317</t>
+          <t>26180522781780006313</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -991,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347341</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MILTON ALONSO</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t xml:space="preserve">PINEDA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOCANEGRA</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,10 +1010,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8136817474</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>8135334064</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CERRO DE LA MITRAS 2855</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1037,52 +1025,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-04-2009</t>
+          <t>18-09-2004</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MILTONALO200478@GMAIL.COM</t>
+          <t>GABRIELPINEDA338@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:53</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>25-02-2026 15:27:11</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:38:51</t>
+          <t>03-03-2026 19:32:56</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:47</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,14 +1090,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522769180006280</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26180522859170006657</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1114,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346395</t>
+          <t>347341</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAVID ALBERTO</t>
+          <t>MILTON ALONSO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>BOCANEGRA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,14 +1157,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8122174357</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>EPIGMENIO GONZALEZ 1626</t>
-        </is>
-      </c>
+          <t>8136817474</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1164,60 +1168,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>12-12-1994</t>
+          <t>20-04-2009</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GALVANALBERTO1994@GMAIL.COM</t>
+          <t>MILTONALO200478@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25-02-2026 08:58:03</t>
+          <t>01-03-2026 12:36:53</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:28</t>
+          <t>01-03-2026 12:38:51</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:14:40</t>
-        </is>
-      </c>
+          <t>31-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1225,18 +1221,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522781930006316</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522769180006280</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1253,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347361</t>
+          <t>346395</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIA CONCEPCION</t>
+          <t>DAVID ALBERTO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RETTA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,67 +1280,63 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8331812722</t>
+          <t>8122174357</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FRESNO 210</t>
+          <t>EPIGMENIO GONZALEZ 1626</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-05-1992</t>
+          <t>12-12-1994</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CONNIRETTA@GMAIL.COM</t>
+          <t>GALVANALBERTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 18:40:28</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:58:03</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 04:12:23</t>
+          <t>02-03-2026 07:16:28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 04:11:38</t>
+          <t>02-03-2026 07:14:40</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1358,7 +1346,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1368,40 +1356,40 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26180522822020006489</t>
+          <t>26180522781930006316</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>347361</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>MARIA CONCEPCION</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>QUIXTIANO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RETTA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,12 +1419,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2381803817</t>
+          <t>8331812722</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VIÑEDO ARGENTINO 313</t>
+          <t>FRESNO 210</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1446,17 +1434,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>23-05-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
+          <t>CONNIRETTA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:32:17</t>
+          <t>01-03-2026 18:40:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,17 +1459,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:38:45</t>
+          <t>03-03-2026 04:12:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1491,7 +1479,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:29</t>
+          <t>03-03-2026 04:11:38</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1501,7 +1489,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1511,36 +1499,40 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26180522807300006437</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26180522822020006489</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347362</t>
+          <t>347648</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89527</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALED </t>
+          <t>MIA YOSELIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,28 +1562,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8180518618</t>
+          <t>8188055318</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-02-2012</t>
+          <t>30-09-2004</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ALEESGN92@GMAIL.COM</t>
+          <t>MREY4604@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-03-2026 21:21:25</t>
+          <t>02-03-2026 15:49:35</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1616,7 +1608,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 15:50:40</t>
+          <t>05-03-2026 16:03:29</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1627,7 +1619,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1638,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522885900006745</t>
+          <t>26180522920130006900</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1654,24 +1646,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347413</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89578</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CLAUDIA ELENA</t>
+          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SEPULVEDA</t>
+          <t>ELIJIO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,7 +1693,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8112123898</t>
+          <t>8116124131</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1712,17 +1704,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-11-1969</t>
+          <t>22-01-1995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SAVY90@HOTMAIL.COM</t>
+          <t>PATTY_ALE22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 07:12:03</t>
+          <t>02-03-2026 16:16:39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1747,12 +1739,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 07:14:01</t>
+          <t>02-03-2026 16:17:52</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1769,7 +1761,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26180522781780006313</t>
+          <t>26180522801020006411</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1793,12 +1785,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347648</t>
+          <t>347973</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>90138</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1800,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MIA YOSELIN</t>
+          <t>ISABEL DEL CARMEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,10 +1820,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8188055318</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>8127472290</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RIO TAMAZUNCHALE 770</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1839,32 +1835,32 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-09-2004</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MREY4604@GMAIL.COM</t>
+          <t>SEGURAGISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 15:49:35</t>
+          <t>03-03-2026 08:47:11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1874,21 +1870,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 16:03:29</t>
+          <t>03-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:49:30</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1896,14 +1900,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26180522920130006900</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522833940006519</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1912,24 +1912,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>347945</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>90110</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ELIJIO</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,33 +1959,33 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8116124131</t>
+          <t>8133810118</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-01-1995</t>
+          <t>03-05-2010</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PATTY_ALE22@HOTMAIL.COM</t>
+          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 16:16:39</t>
+          <t>03-03-2026 07:17:52</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1995,28 +1995,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 16:17:52</t>
+          <t>03-03-2026 07:19:03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2027,36 +2027,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26180522801020006411</t>
+          <t>26180522831500006511</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347945</t>
+          <t>348053</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90110</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,10 +2086,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8133810118</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>8136064783</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN MIGUEL 104</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2097,32 +2101,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-05-2010</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
+          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 07:17:52</t>
+          <t>03-03-2026 13:44:27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2132,21 +2136,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 07:19:03</t>
+          <t>03-03-2026 13:54:18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:53:48</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2154,7 +2166,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26180522831500006511</t>
+          <t>26180522840700006538</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2178,12 +2190,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348053</t>
+          <t>347731</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>89896</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2193,17 +2205,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t xml:space="preserve">ANGEL OSMAR </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2213,12 +2225,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8136064783</t>
+          <t>8136248116</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HACIENDA SAN MIGUEL 104</t>
+          <t>ANTONIO MACHADO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2228,24 +2240,20 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>29-01-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
+          <t>ANGEL.OSMAR13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:44:27</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>02-03-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2253,27 +2261,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:54:18</t>
+          <t>02-03-2026 17:21:56</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:53:48</t>
+          <t>02-03-2026 17:21:32</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2293,14 +2301,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26180522840700006538</t>
+          <t>26180522806130006433</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2317,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348115</t>
+          <t>347415</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90280</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2332,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MELANY AMINADAY</t>
+          <t>JUAN DE DIOS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AMARO</t>
+          <t>CHAGOLLAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>OLAVARRIETA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2352,28 +2360,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8134091393</t>
+          <t>8186811600</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15-02-2007</t>
+          <t>27-08-1983</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
+          <t>JC_F11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:18</t>
+          <t>02-03-2026 07:16:38</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2398,12 +2406,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 16:23:04</t>
+          <t>02-03-2026 07:17:45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26180522846460006583</t>
+          <t>26180522781970006317</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2444,12 +2452,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>348242</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2459,17 +2467,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL OSMAR </t>
+          <t>MELISSA YOSELIN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2479,35 +2487,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8136248116</t>
+          <t>8132524700</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ANTONIO MACHADO</t>
+          <t>DE LA ESCULTURA 1102</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>11-08-1999</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANGEL.OSMAR13@GMAIL.COM</t>
+          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:17</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>03-03-2026 18:46:27</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2515,17 +2527,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:56</t>
+          <t>03-03-2026 18:51:58</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2535,7 +2547,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:32</t>
+          <t>03-03-2026 18:51:15</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2555,14 +2567,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26180522806130006433</t>
+          <t>26180522856500006642</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2579,12 +2591,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347973</t>
+          <t>348480</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90138</t>
+          <t>90645</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2594,17 +2606,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ISABEL DEL CARMEN</t>
+          <t>INGRID</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CEDILLO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2614,14 +2626,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8127472290</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>RIO TAMAZUNCHALE 770</t>
-        </is>
-      </c>
+          <t>8116811694</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2629,32 +2637,32 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>02-02-1998</t>
+          <t>18-09-2007</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SEGURAGISA@GMAIL.COM</t>
+          <t>INGRIDARIAS509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:11</t>
+          <t>04-03-2026 16:22:02</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2664,7 +2672,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:14</t>
+          <t>04-03-2026 16:24:31</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2672,21 +2680,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>03-03-2026 08:49:30</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522833940006519</t>
+          <t>26180522887130006762</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>348452</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90617</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ANGELA VERONICA</t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>URBINA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,47 +2753,43 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8113984035</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>C DE LA PINTURA 1100</t>
-        </is>
-      </c>
+          <t>8123469708</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>05-10-2009</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>AVIG051204@GMAIL.COM</t>
+          <t>JURBINARODRIGU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:11</t>
+          <t>04-03-2026 15:04:34</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2803,7 +2799,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:27</t>
+          <t>04-03-2026 15:05:47</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2811,21 +2807,13 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:48:23</t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2833,7 +2821,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26180522856360006639</t>
+          <t>26180522884370006734</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2857,12 +2845,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348452</t>
+          <t>348115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2872,17 +2860,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>MELANY AMINADAY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>URBINA</t>
+          <t>AMARO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2892,33 +2880,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8123469708</t>
+          <t>8134091393</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05-10-2009</t>
+          <t>15-02-2007</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JURBINARODRIGU@GMAIL.COM</t>
+          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>04-03-2026 15:04:34</t>
+          <t>03-03-2026 16:20:18</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2938,18 +2926,18 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-03-2026 15:05:47</t>
+          <t>03-03-2026 16:23:04</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2960,7 +2948,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26180522884370006734</t>
+          <t>26180522846460006583</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2984,12 +2972,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348674</t>
+          <t>348239</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>90404</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2999,17 +2987,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>ANGELA VERONICA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3019,43 +3007,47 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8148715957</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>8113984035</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C DE LA PINTURA 1100</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-09-2003</t>
+          <t>05-12-2004</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CG028887@GMAIL.COM</t>
+          <t>AVIG051204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-03-2026 12:04:41</t>
+          <t>03-03-2026 18:43:11</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3065,21 +3057,29 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-03-2026 12:05:48</t>
+          <t>03-03-2026 18:49:27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:48:23</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26180522914190006861</t>
+          <t>26180522856360006639</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3111,12 +3111,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348762</t>
+          <t>348674</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>90839</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CYNTHIA BEATRIZ</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MONTIEL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3146,79 +3146,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8121933568</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>PASEO DEL MILAGRO 1027</t>
-        </is>
-      </c>
+          <t>8148715957</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31-03-2007</t>
+          <t>05-09-2003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
+          <t>CG028887@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-03-2026 17:07:33</t>
+          <t>05-03-2026 12:04:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-03-2026 17:22:45</t>
+          <t>05-03-2026 12:05:48</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>05-03-2026 17:20:29</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3226,18 +3214,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26180522923710006941</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522914190006861</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3254,12 +3238,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348242</t>
+          <t>348762</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>90927</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3269,17 +3253,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MELISSA YOSELIN</t>
+          <t>CYNTHIA BEATRIZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CORTES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MONTIEL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3289,12 +3273,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8132524700</t>
+          <t>8121933568</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DE LA ESCULTURA 1102</t>
+          <t>PASEO DEL MILAGRO 1027</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3304,52 +3288,52 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11-08-1999</t>
+          <t>31-03-2007</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:46:27</t>
+          <t>05-03-2026 17:07:33</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:58</t>
+          <t>05-03-2026 17:22:45</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:15</t>
+          <t>05-03-2026 17:20:29</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3369,36 +3353,40 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26180522856500006642</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26180522923710006941</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348480</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90645</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,17 +3396,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>INGRID</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>QUIXTIANO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CEDILLO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3428,10 +3416,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8116811694</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>2381803817</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>VIÑEDO ARGENTINO 313</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3439,56 +3431,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-09-2007</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>INGRIDARIAS509@GMAIL.COM</t>
+          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-03-2026 16:22:02</t>
+          <t>02-03-2026 17:32:17</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-03-2026 16:24:31</t>
+          <t>02-03-2026 17:38:45</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:37:29</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3496,14 +3496,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26180522887130006762</t>
+          <t>26180522807300006437</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3514,6 +3514,129 @@
       <c r="AC23" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348872</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91037</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MAXIMILIANO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MEDRANO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GRANADOS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8125236003</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>06-02-2004</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MAXMEDRANO36@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:28:23</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:29:16</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26180522946370007007</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Aurora Nohemi Juarez Garza</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347362</t>
+          <t>195940</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89527</t>
+          <t>93447</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALED </t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,10 +752,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8180518618</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>8126293113</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SIERRA DE SAN CRISTOBAL 124</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -763,32 +767,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15-02-2012</t>
+          <t>08-11-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ALEESGN92@GMAIL.COM</t>
+          <t>JUAREZMARTINEZJOSEANTONIO500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 21:21:25</t>
+          <t>11-09-2023 08:06:08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -798,21 +802,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 15:50:40</t>
+          <t>09-03-2026 15:36:27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:35:55</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,14 +832,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180522885900006745</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180523011720007237</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -836,24 +844,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347413</t>
+          <t>336271</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89578</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CLAUDIA ELENA</t>
+          <t>ALEXANDER GABRIEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEPULVEDA</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,35 +891,31 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8112123898</t>
+          <t>8132249255</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24-11-1969</t>
+          <t>04-02-2012</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SAVY90@HOTMAIL.COM</t>
+          <t>ALEXANDER83618@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:12:03</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>20-01-2026 06:22:09</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -919,22 +923,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:14:01</t>
+          <t>16-03-2026 08:02:30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>15-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -951,14 +955,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26180522781780006313</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26180523203880008042</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346506</t>
+          <t>347362</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t xml:space="preserve">ALED </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PINEDA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,14 +1022,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8135334064</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CERRO DE LA MITRAS 2855</t>
-        </is>
-      </c>
+          <t>8180518618</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1025,32 +1033,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18-09-2004</t>
+          <t>15-02-2012</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>GABRIELPINEDA338@GMAIL.COM</t>
+          <t>ALEESGN92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25-02-2026 15:27:11</t>
+          <t>01-03-2026 21:21:25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1060,29 +1068,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:56</t>
+          <t>04-03-2026 15:50:40</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:31:47</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,19 +1090,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522859170006657</t>
+          <t>26180522885900006745</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1110,24 +1106,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aurora Nohemi Juarez Garza</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347341</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MILTON ALONSO</t>
+          <t>CLAUDIA ELENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>SEPULVEDA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOCANEGRA</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,31 +1153,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8136817474</t>
+          <t>8112123898</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-04-2009</t>
+          <t>24-11-1969</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MILTONALO200478@GMAIL.COM</t>
+          <t>SAVY90@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:53</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>02-03-2026 07:12:03</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1189,22 +1189,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:38:51</t>
+          <t>02-03-2026 07:14:01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>31-05-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1221,14 +1221,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522769180006280</t>
+          <t>26180522781780006313</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1527,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347648</t>
+          <t>347341</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIA YOSELIN</t>
+          <t>MILTON ALONSO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>BOCANEGRA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,35 +1562,31 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8188055318</t>
+          <t>8136817474</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-09-2004</t>
+          <t>20-04-2009</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MREY4604@GMAIL.COM</t>
+          <t>MILTONALO200478@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 15:49:35</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>01-03-2026 12:36:53</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1598,22 +1594,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 16:03:29</t>
+          <t>01-03-2026 12:38:51</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1630,18 +1626,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522920130006900</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180522769180006280</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1658,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ELIJIO</t>
+          <t xml:space="preserve">PINEDA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,67 +1685,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8116124131</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>8135334064</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CERRO DE LA MITRAS 2855</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-01-1995</t>
+          <t>18-09-2004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PATTY_ALE22@HOTMAIL.COM</t>
+          <t>GABRIELPINEDA338@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:16:39</t>
+          <t>25-02-2026 15:27:11</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:17:52</t>
+          <t>03-03-2026 19:32:56</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:47</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1761,14 +1765,22 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26180522801020006411</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26180522859170006657</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1785,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347973</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90138</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1800,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ISABEL DEL CARMEN</t>
+          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>ELIJIO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1820,14 +1832,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8127472290</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>RIO TAMAZUNCHALE 770</t>
-        </is>
-      </c>
+          <t>8116124131</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1835,64 +1843,56 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-02-1998</t>
+          <t>22-01-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SEGURAGISA@GMAIL.COM</t>
+          <t>PATTY_ALE22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:11</t>
+          <t>02-03-2026 16:16:39</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:14</t>
+          <t>02-03-2026 16:17:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-03-2026 08:49:30</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1900,19 +1900,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26180522833940006519</t>
+          <t>26180522801020006411</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347945</t>
+          <t>347648</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90110</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t>MIA YOSELIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,33 +1959,33 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8133810118</t>
+          <t>8188055318</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>03-05-2010</t>
+          <t>30-09-2004</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
+          <t>MREY4604@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 07:17:52</t>
+          <t>02-03-2026 15:49:35</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2005,18 +2005,18 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 07:19:03</t>
+          <t>05-03-2026 16:03:29</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2027,10 +2027,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26180522831500006511</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26180522920130006900</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2039,7 +2043,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2051,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348053</t>
+          <t>347415</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2070,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>JUAN DE DIOS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>CHAGOLLAN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>OLAVARRIETA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,14 +2090,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8136064783</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>HACIENDA SAN MIGUEL 104</t>
-        </is>
-      </c>
+          <t>8186811600</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2101,32 +2101,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>27-08-1983</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
+          <t>JC_F11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 13:44:27</t>
+          <t>02-03-2026 07:16:38</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2136,29 +2136,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 13:54:18</t>
+          <t>02-03-2026 07:17:45</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-03-2026 13:53:48</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2166,7 +2158,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26180522840700006538</t>
+          <t>26180522781970006317</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2190,12 +2182,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347731</t>
+          <t>347945</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89896</t>
+          <t>90110</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2205,17 +2197,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL OSMAR </t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2225,14 +2217,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8136248116</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ANTONIO MACHADO</t>
-        </is>
-      </c>
+          <t>8133810118</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2240,60 +2228,56 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>03-05-2010</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ANGEL.OSMAR13@GMAIL.COM</t>
+          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:17</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>03-03-2026 07:17:52</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 17:21:56</t>
+          <t>03-03-2026 07:19:03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:21:32</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2301,36 +2285,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26180522806130006433</t>
+          <t>26180522831500006511</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347415</t>
+          <t>347731</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89580</t>
+          <t>89896</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2324,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JUAN DE DIOS</t>
+          <t xml:space="preserve">ANGEL OSMAR </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CHAGOLLAN</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OLAVARRIETA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,10 +2344,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8186811600</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>8136248116</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ANTONIO MACHADO</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2371,42 +2359,38 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27-08-1983</t>
+          <t>29-01-2000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JC_F11@HOTMAIL.COM</t>
+          <t>ANGEL.OSMAR13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:38</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Convenio 99</t>
-        </is>
-      </c>
+          <t>02-03-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 07:17:45</t>
+          <t>02-03-2026 17:21:56</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2414,13 +2398,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:21:32</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2428,14 +2420,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26180522781970006317</t>
+          <t>26180522806130006433</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2452,12 +2444,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348242</t>
+          <t>347973</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>90138</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2467,17 +2459,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MELISSA YOSELIN</t>
+          <t>ISABEL DEL CARMEN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2487,12 +2479,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8132524700</t>
+          <t>8127472290</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DE LA ESCULTURA 1102</t>
+          <t>RIO TAMAZUNCHALE 770</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2502,17 +2494,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11-08-1999</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+          <t>SEGURAGISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:46:27</t>
+          <t>03-03-2026 08:47:11</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2537,7 +2529,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:58</t>
+          <t>03-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2547,7 +2539,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:15</t>
+          <t>03-03-2026 08:49:30</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2567,7 +2559,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26180522856500006642</t>
+          <t>26180522833940006519</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2579,24 +2571,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348480</t>
+          <t>348053</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90645</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2606,17 +2598,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>INGRID</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CEDILLO</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2626,43 +2618,47 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8116811694</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>8136064783</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN MIGUEL 104</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-09-2007</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>INGRIDARIAS509@GMAIL.COM</t>
+          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 16:22:02</t>
+          <t>03-03-2026 13:44:27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2672,21 +2668,29 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 16:24:31</t>
+          <t>03-03-2026 13:54:18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:53:48</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2694,7 +2698,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522887130006762</t>
+          <t>26180522840700006538</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2718,12 +2722,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348452</t>
+          <t>348115</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2737,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>MELANY AMINADAY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>URBINA</t>
+          <t>AMARO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,33 +2757,33 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8123469708</t>
+          <t>8134091393</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>05-10-2009</t>
+          <t>15-02-2007</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JURBINARODRIGU@GMAIL.COM</t>
+          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-03-2026 15:04:34</t>
+          <t>03-03-2026 16:20:18</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2799,18 +2803,18 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-03-2026 15:05:47</t>
+          <t>03-03-2026 16:23:04</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2821,7 +2825,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26180522884370006734</t>
+          <t>26180522846460006583</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2845,12 +2849,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348115</t>
+          <t>348239</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90280</t>
+          <t>90404</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2860,17 +2864,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MELANY AMINADAY</t>
+          <t>ANGELA VERONICA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AMARO</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2880,10 +2884,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8134091393</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>8113984035</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C DE LA PINTURA 1100</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2891,32 +2899,32 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-02-2007</t>
+          <t>05-12-2004</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
+          <t>AVIG051204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:18</t>
+          <t>03-03-2026 18:43:11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2926,7 +2934,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 16:23:04</t>
+          <t>03-03-2026 18:49:27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2934,13 +2942,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:48:23</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2948,7 +2964,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26180522846460006583</t>
+          <t>26180522856360006639</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2972,12 +2988,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>348242</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2987,17 +3003,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANGELA VERONICA</t>
+          <t>MELISSA YOSELIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3007,12 +3023,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8113984035</t>
+          <t>8132524700</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C DE LA PINTURA 1100</t>
+          <t>DE LA ESCULTURA 1102</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3022,17 +3038,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>11-08-1999</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AVIG051204@GMAIL.COM</t>
+          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:11</t>
+          <t>03-03-2026 18:46:27</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3057,7 +3073,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:27</t>
+          <t>03-03-2026 18:51:58</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3067,7 +3083,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:48:23</t>
+          <t>03-03-2026 18:51:15</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3077,7 +3093,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3087,7 +3103,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26180522856360006639</t>
+          <t>26180522856500006642</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3099,24 +3115,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348674</t>
+          <t>348480</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>90645</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3126,17 +3142,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>INGRID</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CEDILLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3146,28 +3162,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8148715957</t>
+          <t>8116811694</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>05-09-2003</t>
+          <t>18-09-2007</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CG028887@GMAIL.COM</t>
+          <t>INGRIDARIAS509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-03-2026 12:04:41</t>
+          <t>04-03-2026 16:22:02</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3192,18 +3208,18 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-03-2026 12:05:48</t>
+          <t>04-03-2026 16:24:31</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3214,7 +3230,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26180522914190006861</t>
+          <t>26180522887130006762</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3238,12 +3254,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348762</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3253,17 +3269,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CYNTHIA BEATRIZ</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t>QUIXTIANO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MONTIEL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3273,12 +3289,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8121933568</t>
+          <t>2381803817</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PASEO DEL MILAGRO 1027</t>
+          <t>VIÑEDO ARGENTINO 313</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3288,17 +3304,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31-03-2007</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
+          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>05-03-2026 17:07:33</t>
+          <t>02-03-2026 17:32:17</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3313,27 +3329,27 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-03-2026 17:22:45</t>
+          <t>02-03-2026 17:38:45</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>05-03-2026 17:20:29</t>
+          <t>02-03-2026 17:37:29</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3343,7 +3359,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3353,40 +3369,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26180522923710006941</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522807300006437</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>348452</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>90617</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3396,17 +3408,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>QUIXTIANO</t>
+          <t>URBINA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3416,79 +3428,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2381803817</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>VIÑEDO ARGENTINO 313</t>
-        </is>
-      </c>
+          <t>8123469708</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>05-10-2009</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
+          <t>JURBINARODRIGU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:32:17</t>
+          <t>04-03-2026 15:04:34</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:38:45</t>
+          <t>04-03-2026 15:05:47</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:37:29</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3496,14 +3496,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26180522807300006437</t>
+          <t>26180522884370006734</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3637,6 +3637,2606 @@
       <c r="AC24" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348674</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90839</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8148715957</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>05-09-2003</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CG028887@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:04:41</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:05:48</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26180522914190006861</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348762</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90927</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CYNTHIA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CORTES</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MONTIEL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>8121933568</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PASEO DEL MILAGRO 1027</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>31-03-2007</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:07:33</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:22:45</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:20:29</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26180522923710006941</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Eduardo Alejandro Garcia Dimas</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349653</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>91818</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MIRIAM EDITH</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTOBAL </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>8123234107</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>21-05-1978</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>EDITH@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:11:53</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:13:42</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26180523026390007333</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349690</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91855</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BRANDON ANDRES</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HUERTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>8110636274</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C LA MANCHA 418</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>21-05-2003</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>BCASTILLOHUERTA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:47:55</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:04:50</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:03:09</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26180523133450007809</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Aurora Nohemi Juarez Garza</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349895</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>92060</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>8135935513</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>07-09-2004</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DAAVIIDSIILVAA55@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:06:04</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>12-03-2026 16:32:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26180523126440007753</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Eduardo Alejandro Garcia Dimas</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>350348</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92512</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JUAN PAULO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NIÑO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>8123083411</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>04-01-2011</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>JPAULO.VALENZ04@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:39:04</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:42:10</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>11-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26180523123810007729</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>350032</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92197</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAMUEL </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MARTIR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8684643209</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>08-07-2004</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>SAMUELMARTIR5@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>11-03-2026 06:43:40</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>11-03-2026 06:50:08</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26180523081610007553</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>350326</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>92490</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DANTE AUGUSTO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MACIAS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>URBINAS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8112456466</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>03-02-2008</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DANTEAMO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:26:54</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>12-03-2026 13:28:07</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26180523122320007723</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351067</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93231</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ZAIRA MARIBEL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>8144314757</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25-03-2003</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ZAIRATORRES000@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:20:34</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:21:55</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26180523214540008065</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>351185</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93349</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA BELEN </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>8180247441</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LOMAS DE SANTA CATARINA 338</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>16-03-1983</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MARIABELENLOPEZSOTO1983@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:35:39</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:39:15</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:38:39</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26180523222060008093</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>350674</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>92838</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA CRISTINA </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GASCA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>8130992205</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SAN AGUSTIN 113</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>23-10-1999</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ANA.GARCIAGSC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:15:41</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:20:20</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:19:29</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26180523162710007924</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>350812</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>92976</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>JULIO CESAR</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAN MARTIN </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MENDEZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>8128718023</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>29-09-2007</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>MENDEZJULIOCESAR007@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>14-03-2026 13:06:38</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>14-03-2026 13:09:01</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>13-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26180523184000007990</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>351478</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>93642</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HERMIONE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CARDOZA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>8125978834</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>18-11-2010</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>HERMIONE181110@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:23:15</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:24:21</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26180523251560008181</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Jose Armando  Armijo Campos</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>351935</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>94099</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ERIKA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>8130742688</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14-03-1982</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ERICKA8214@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:14:55</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:18:17</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26180523302540008390</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>351480</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>93644</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PRIA CONSTANZA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GALVAN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8130805757</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15-09-2010</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PRIAALVARADO425@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:26:13</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:27:54</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26180523251640008182</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Jose Armando  Armijo Campos</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>351068</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>93232</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>KELVIN IVAN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RANGEL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FONSECA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8136397105</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10-10-2000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>KELVINRF00@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:23:24</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:24:56</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26180523214650008066</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>351209</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>93373</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TAMARA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RETTA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HERNADNEZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8117940617</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>07-11-2010</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>TAMARARETTAHDZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:23:46</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:03:46</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26180523268300008263</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>351714</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>93878</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>REGINA YAMILETH</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8124422040</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>28-11-2002</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>YAMIREGI@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:23:05</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:24:17</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26180523273430008281</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>351929</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>94093</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESIA </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ESTEBAN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8131387457</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>23-08-2011</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ESTEBANREYESFRESIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:11:21</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>18-03-2026 18:20:15</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26180523302630008391</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>351325</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>93489</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DIEGO YOTUEL</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BRIONES</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>RIVAS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>8112803747</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SIERRA PAPAGAYOS 1128</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>16-01-2002</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>DIEGOYOTUEL09@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:03:22</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:53:02</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:51:41</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26180523310530008423</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__STA CATARINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301839</t>
+          <t>336271</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99337</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>ALEXANDER GABRIEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,14 +613,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8119155852</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ANTONIO MACHADO 2953</t>
-        </is>
-      </c>
+          <t>8132249255</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -628,60 +624,52 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02-09-1993</t>
+          <t>04-02-2012</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CERDAJAIME75@GMAIL.COM</t>
+          <t>ALEXANDER83618@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-07-2025 19:04:12</t>
+          <t>20-01-2026 06:22:09</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:38</t>
+          <t>16-03-2026 08:02:30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:15:49</t>
-        </is>
-      </c>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,40 +677,44 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26180522805690006432</t>
+          <t>26180523203880008042</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>301839</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93447</t>
+          <t>99337</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +744,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8126293113</t>
+          <t>8119155852</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SIERRA DE SAN CRISTOBAL 124</t>
+          <t>ANTONIO MACHADO 2953</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,24 +759,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>08-11-2005</t>
+          <t>02-09-1993</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>JUAREZMARTINEZJOSEANTONIO500@GMAIL.COM</t>
+          <t>CERDAJAIME75@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11-09-2023 08:06:08</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>02-07-2025 19:04:12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -792,27 +780,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>09-03-2026 15:36:27</t>
+          <t>02-03-2026 17:16:38</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>09-03-2026 15:35:55</t>
+          <t>02-03-2026 17:15:49</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,36 +820,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26180523011720007237</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26180522805690006432</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>336271</t>
+          <t>305266</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALEXANDER GABRIEL</t>
+          <t>ADRIANA CAMILA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,31 +883,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8132249255</t>
+          <t>4811221580</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>04-02-2012</t>
+          <t>11-11-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEXANDER83618@GMAIL.COM</t>
+          <t>ADRIANACAMILAMEDINA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>20-01-2026 06:22:09</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>22-07-2025 06:16:42</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -923,22 +919,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-03-2026 08:02:30</t>
+          <t>30-03-2026 11:07:12</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
+          <t>29-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -955,22 +951,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26180523203880008042</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>LILIANA SARAHI MORALES VARGAS</t>
-        </is>
-      </c>
+          <t>26180523624260009609</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -987,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347362</t>
+          <t>195940</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89527</t>
+          <t>93447</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALED </t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,10 +1010,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8180518618</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>8126293113</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SIERRA DE SAN CRISTOBAL 124</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1033,32 +1025,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-02-2012</t>
+          <t>08-11-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ALEESGN92@GMAIL.COM</t>
+          <t>JUAREZMARTINEZJOSEANTONIO500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 21:21:25</t>
+          <t>11-09-2023 08:06:08</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1068,21 +1060,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>04-03-2026 15:50:40</t>
+          <t>09-03-2026 15:36:27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:35:55</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,14 +1090,10 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26180522885900006745</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180523011720007237</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1106,24 +1102,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Aurora Nohemi Juarez Garza</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347413</t>
+          <t>346395</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89578</t>
+          <t>88560</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLAUDIA ELENA</t>
+          <t>DAVID ALBERTO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEPULVEDA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GARZA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,67 +1149,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8112123898</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>8122174357</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EPIGMENIO GONZALEZ 1626</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-11-1969</t>
+          <t>12-12-1994</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SAVY90@HOTMAIL.COM</t>
+          <t>GALVANALBERTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:12:03</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:58:03</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:14:01</t>
+          <t>02-03-2026 07:16:28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:14:40</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,36 +1225,40 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26180522781780006313</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26180522781930006316</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>346395</t>
+          <t>347341</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DAVID ALBERTO</t>
+          <t>MILTON ALONSO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>BOCANEGRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,14 +1288,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8122174357</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>EPIGMENIO GONZALEZ 1626</t>
-        </is>
-      </c>
+          <t>8136817474</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1295,60 +1299,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-12-1994</t>
+          <t>20-04-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GALVANALBERTO1994@GMAIL.COM</t>
+          <t>MILTONALO200478@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25-02-2026 08:58:03</t>
+          <t>01-03-2026 12:36:53</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:28</t>
+          <t>01-03-2026 12:38:51</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:14:40</t>
-        </is>
-      </c>
+          <t>31-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1356,40 +1352,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26180522781930006316</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522769180006280</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347361</t>
+          <t>345187</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89526</t>
+          <t>87352</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIA CONCEPCION</t>
+          <t xml:space="preserve">RUTH </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RETTA</t>
+          <t>MUÑIZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,12 +1411,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8331812722</t>
+          <t>8131139395</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRESNO 210</t>
+          <t>AND DE LA SOCIEDAD 109</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1434,17 +1426,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-05-1992</t>
+          <t>07-01-1973</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CONNIRETTA@GMAIL.COM</t>
+          <t>RYTH_MB7@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-03-2026 18:40:28</t>
+          <t>19-02-2026 19:06:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1469,17 +1461,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 04:12:23</t>
+          <t>30-03-2026 20:07:02</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>29-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 04:11:38</t>
+          <t>30-03-2026 20:06:06</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1499,15 +1491,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26180522822020006489</t>
+          <t>26180523649730009754</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>649</t>
@@ -1515,24 +1511,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347341</t>
+          <t>347361</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MILTON ALONSO</t>
+          <t>MARIA CONCEPCION</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOCANEGRA</t>
+          <t>RETTA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,63 +1558,79 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8136817474</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>8331812722</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FRESNO 210</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20-04-2009</t>
+          <t>23-05-1992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MILTONALO200478@GMAIL.COM</t>
+          <t>CONNIRETTA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:53</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>01-03-2026 18:40:28</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-03-2026 12:38:51</t>
+          <t>03-03-2026 04:12:23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>31-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 04:11:38</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1626,36 +1638,40 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26180522769180006280</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26180522822020006489</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>346506</t>
+          <t>347415</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>JUAN DE DIOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PINEDA </t>
+          <t>CHAGOLLAN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>OLAVARRIETA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,14 +1701,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8135334064</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CERRO DE LA MITRAS 2855</t>
-        </is>
-      </c>
+          <t>8186811600</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1700,32 +1712,32 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18-09-2004</t>
+          <t>27-08-1983</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GABRIELPINEDA338@GMAIL.COM</t>
+          <t>JC_F11@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25-02-2026 15:27:11</t>
+          <t>02-03-2026 07:16:38</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1735,29 +1747,21 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 19:32:56</t>
+          <t>02-03-2026 07:17:45</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:31:47</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1765,19 +1769,11 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26180522859170006657</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>CAROLINA ZUÑIGA MARTINEZ</t>
-        </is>
-      </c>
+          <t>26180522781970006317</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1797,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>347648</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
+          <t>MIA YOSELIN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ELIJIO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,7 +1828,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8116124131</t>
+          <t>8188055318</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1843,22 +1839,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-01-1995</t>
+          <t>30-09-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PATTY_ALE22@HOTMAIL.COM</t>
+          <t>MREY4604@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 16:16:39</t>
+          <t>02-03-2026 15:49:35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1868,22 +1864,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 16:17:52</t>
+          <t>05-03-2026 16:03:29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1900,14 +1896,18 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26180522801020006411</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26180522920130006900</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347648</t>
+          <t>346506</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MIA YOSELIN</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t xml:space="preserve">PINEDA </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,43 +1959,47 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8188055318</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>8135334064</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CERRO DE LA MITRAS 2855</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30-09-2004</t>
+          <t>18-09-2004</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MREY4604@GMAIL.COM</t>
+          <t>GABRIELPINEDA338@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 15:49:35</t>
+          <t>25-02-2026 15:27:11</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2005,21 +2009,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-03-2026 16:03:29</t>
+          <t>03-03-2026 19:32:56</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:31:47</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2027,15 +2039,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26180522920130006900</t>
+          <t>26180522859170006657</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2043,24 +2059,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347415</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89580</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2070,17 +2086,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JUAN DE DIOS</t>
+          <t xml:space="preserve">PATRICIA ALEJANDRA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CHAGOLLAN</t>
+          <t>ELIJIO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OLAVARRIETA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2090,33 +2106,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8186811600</t>
+          <t>8116124131</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27-08-1983</t>
+          <t>22-01-1995</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JC_F11@HOTMAIL.COM</t>
+          <t>PATTY_ALE22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:16:38</t>
+          <t>02-03-2026 16:16:39</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2126,22 +2142,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 07:17:45</t>
+          <t>02-03-2026 16:17:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2158,36 +2174,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26180522781970006317</t>
+          <t>26180522801020006411</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347945</t>
+          <t>347362</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90110</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2197,17 +2213,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MAURICIO</t>
+          <t xml:space="preserve">ALED </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2217,7 +2233,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8133810118</t>
+          <t>8180518618</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2228,22 +2244,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-05-2010</t>
+          <t>15-02-2012</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
+          <t>ALEESGN92@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 07:17:52</t>
+          <t>01-03-2026 21:21:25</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2263,12 +2279,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 07:19:03</t>
+          <t>04-03-2026 15:50:40</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2285,10 +2301,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26180522831500006511</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26180522885900006745</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2297,7 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>Aurora Nohemi Juarez Garza</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2444,12 +2464,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347973</t>
+          <t>347747</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90138</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2459,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ISABEL DEL CARMEN</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>QUIXTIANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2479,12 +2499,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8127472290</t>
+          <t>2381803817</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>RIO TAMAZUNCHALE 770</t>
+          <t>VIÑEDO ARGENTINO 313</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2494,52 +2514,52 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02-02-1998</t>
+          <t>03-04-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SEGURAGISA@GMAIL.COM</t>
+          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:11</t>
+          <t>02-03-2026 17:32:17</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:14</t>
+          <t>02-03-2026 17:38:45</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:49:30</t>
+          <t>02-03-2026 17:37:29</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2549,7 +2569,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2559,36 +2579,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26180522833940006519</t>
+          <t>26180522807300006437</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348053</t>
+          <t>348029</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>90194</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2598,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t xml:space="preserve">JAVIER DE JESUS </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MELENDEZ</t>
+          <t>ALEMAN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2618,12 +2638,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8136064783</t>
+          <t>8116627887</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HACIENDA SAN MIGUEL 104</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2633,17 +2653,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10-06-1994</t>
+          <t>17-09-1994</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
+          <t>JAVIERALEMAN2008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 13:44:27</t>
+          <t>03-03-2026 12:31:36</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2668,17 +2688,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 13:54:18</t>
+          <t>24-03-2026 09:48:05</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-03-2026 13:53:48</t>
+          <t>24-03-2026 09:47:21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2698,11 +2718,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26180522840700006538</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26180523462410008968</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -2722,12 +2750,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348115</t>
+          <t>348242</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90280</t>
+          <t>90407</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2737,17 +2765,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MELANY AMINADAY</t>
+          <t>MELISSA YOSELIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AMARO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ONTIVEROS</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2757,10 +2785,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8134091393</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>8132524700</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>DE LA ESCULTURA 1102</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2768,32 +2800,32 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-02-2007</t>
+          <t>11-08-1999</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
+          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:18</t>
+          <t>03-03-2026 18:46:27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2803,7 +2835,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 16:23:04</t>
+          <t>03-03-2026 18:51:58</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2811,13 +2843,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:51:15</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2825,7 +2865,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26180522846460006583</t>
+          <t>26180522856500006642</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2837,24 +2877,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>347973</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90138</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2864,17 +2904,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ANGELA VERONICA</t>
+          <t>ISABEL DEL CARMEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2884,12 +2924,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8113984035</t>
+          <t>8127472290</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C DE LA PINTURA 1100</t>
+          <t>RIO TAMAZUNCHALE 770</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2899,17 +2939,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>AVIG051204@GMAIL.COM</t>
+          <t>SEGURAGISA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:11</t>
+          <t>03-03-2026 08:47:11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2934,7 +2974,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:27</t>
+          <t>03-03-2026 08:50:14</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2944,7 +2984,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-03-2026 18:48:23</t>
+          <t>03-03-2026 08:49:30</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2954,7 +2994,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2964,7 +3004,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26180522856360006639</t>
+          <t>26180522833940006519</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2976,24 +3016,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348242</t>
+          <t>348480</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90407</t>
+          <t>90645</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +3043,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MELISSA YOSELIN</t>
+          <t>INGRID</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CEDILLO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,14 +3063,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8132524700</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>DE LA ESCULTURA 1102</t>
-        </is>
-      </c>
+          <t>8116811694</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3038,32 +3074,32 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11-08-1999</t>
+          <t>18-09-2007</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MELISSAALVAREZ110899@GMAIL.COM</t>
+          <t>INGRIDARIAS509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:46:27</t>
+          <t>04-03-2026 16:22:02</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3073,29 +3109,21 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 18:51:58</t>
+          <t>04-03-2026 16:24:31</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:51:15</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3103,7 +3131,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26180522856500006642</t>
+          <t>26180522887130006762</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3115,24 +3143,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348480</t>
+          <t>347945</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90645</t>
+          <t>90110</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3142,17 +3170,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>INGRID</t>
+          <t>MAURICIO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CEDILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3162,33 +3190,33 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8116811694</t>
+          <t>8133810118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18-09-2007</t>
+          <t>03-05-2010</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>INGRIDARIAS509@GMAIL.COM</t>
+          <t>CAMACHOCASTROMAURICIO362@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-03-2026 16:22:02</t>
+          <t>03-03-2026 07:17:52</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3208,18 +3236,18 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 16:24:31</t>
+          <t>03-03-2026 07:19:03</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3230,7 +3258,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26180522887130006762</t>
+          <t>26180522831500006511</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3242,24 +3270,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347747</t>
+          <t>348053</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3269,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>QUIXTIANO</t>
+          <t>MELENDEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3289,67 +3317,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2381803817</t>
+          <t>8136064783</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VIÑEDO ARGENTINO 313</t>
+          <t>HACIENDA SAN MIGUEL 104</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-04-2002</t>
+          <t>10-06-1994</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MARIANAQUIXTIANOTORRES55@GMAIL.COM</t>
+          <t>ALEJANDROMELENDEZVILLA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:32:17</t>
+          <t>03-03-2026 13:44:27</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:38:45</t>
+          <t>03-03-2026 13:54:18</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:29</t>
+          <t>03-03-2026 13:53:48</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3359,7 +3387,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3369,14 +3397,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26180522807300006437</t>
+          <t>26180522840700006538</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3393,12 +3421,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348452</t>
+          <t>348115</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,17 +3436,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>MELANY AMINADAY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>URBINA</t>
+          <t>AMARO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ONTIVEROS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3428,33 +3456,33 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8123469708</t>
+          <t>8134091393</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>05-10-2009</t>
+          <t>15-02-2007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JURBINARODRIGU@GMAIL.COM</t>
+          <t>ANARIONTIVEROSMELANYAMINADAY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-03-2026 15:04:34</t>
+          <t>03-03-2026 16:20:18</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3474,18 +3502,18 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-03-2026 15:05:47</t>
+          <t>03-03-2026 16:23:04</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3496,7 +3524,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26180522884370006734</t>
+          <t>26180522846460006583</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3520,12 +3548,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348872</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>91037</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3535,17 +3563,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MAXIMILIANO</t>
+          <t>CLAUDIA ELENA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>SEPULVEDA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GRANADOS</t>
+          <t>GARZA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3555,31 +3583,35 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8125236003</t>
+          <t>8112123898</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>06-02-2004</t>
+          <t>24-11-1969</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MAXMEDRANO36@GMAIL.COM</t>
+          <t>SAVY90@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>06-03-2026 10:28:23</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>02-03-2026 07:12:03</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3587,22 +3619,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-03-2026 10:29:16</t>
+          <t>02-03-2026 07:14:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3619,36 +3651,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26180522946370007007</t>
+          <t>26180522781780006313</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Aurora Nohemi Juarez Garza</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348674</t>
+          <t>348452</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>90617</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3658,17 +3690,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>URBINA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3678,7 +3710,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8148715957</t>
+          <t>8123469708</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3689,17 +3721,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>05-09-2003</t>
+          <t>05-10-2009</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CG028887@GMAIL.COM</t>
+          <t>JURBINARODRIGU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>05-03-2026 12:04:41</t>
+          <t>04-03-2026 15:04:34</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3724,12 +3756,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>05-03-2026 12:05:48</t>
+          <t>04-03-2026 15:05:47</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3746,7 +3778,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26180522914190006861</t>
+          <t>26180522884370006734</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3770,12 +3802,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348762</t>
+          <t>348674</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>90839</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3785,17 +3817,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CYNTHIA BEATRIZ</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CORTES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MONTIEL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3805,57 +3837,53 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8121933568</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>PASEO DEL MILAGRO 1027</t>
-        </is>
-      </c>
+          <t>8148715957</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31-03-2007</t>
+          <t>05-09-2003</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
+          <t>CG028887@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-03-2026 17:07:33</t>
+          <t>05-03-2026 12:04:41</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-03-2026 17:22:45</t>
+          <t>05-03-2026 12:05:48</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3863,21 +3891,13 @@
           <t>04-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>05-03-2026 17:20:29</t>
-        </is>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3885,40 +3905,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26180522923710006941</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26180522914190006861</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Eduardo Alejandro Garcia Dimas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>349653</t>
+          <t>348239</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>90404</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3928,17 +3944,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MIRIAM EDITH</t>
+          <t>ANGELA VERONICA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTOBAL </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3948,10 +3964,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8123234107</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>8113984035</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C DE LA PINTURA 1100</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3959,56 +3979,64 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-05-1978</t>
+          <t>05-12-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EDITH@ICLOUD.COM</t>
+          <t>AVIG051204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-03-2026 19:11:53</t>
+          <t>03-03-2026 18:43:11</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-03-2026 19:13:42</t>
+          <t>03-03-2026 18:49:27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:48:23</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4016,14 +4044,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26180523026390007333</t>
+          <t>26180522856360006639</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4187,12 +4215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349895</t>
+          <t>348762</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>92060</t>
+          <t>90927</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4202,17 +4230,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>CYNTHIA BEATRIZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CORTES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
+          <t>MONTIEL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4222,67 +4250,79 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8135935513</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>8121933568</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PASEO DEL MILAGRO 1027</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>07-09-2004</t>
+          <t>31-03-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DAAVIIDSIILVAA55@GMAIL.COM</t>
+          <t>BEATRIZMONTIEL031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-03-2026 17:06:04</t>
+          <t>05-03-2026 17:07:33</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-03-2026 16:32:10</t>
+          <t>05-03-2026 17:22:45</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:20:29</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4290,18 +4330,18 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26180523126440007753</t>
+          <t>26180522923710006941</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4318,12 +4358,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>350348</t>
+          <t>348872</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92512</t>
+          <t>91037</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4333,17 +4373,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JUAN PAULO</t>
+          <t>MAXIMILIANO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NIÑO</t>
+          <t>GRANADOS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4353,7 +4393,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8123083411</t>
+          <t>8125236003</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4364,17 +4404,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>04-01-2011</t>
+          <t>06-02-2004</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JPAULO.VALENZ04@GMAIL.COM</t>
+          <t>MAXMEDRANO36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12-03-2026 14:39:04</t>
+          <t>06-03-2026 10:28:23</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4395,12 +4435,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>12-03-2026 14:42:10</t>
+          <t>06-03-2026 10:29:16</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>11-06-2026 23:59:59</t>
+          <t>05-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4417,7 +4457,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26180523123810007729</t>
+          <t>26180522946370007007</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4429,24 +4469,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aurora Nohemi Juarez Garza</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>350032</t>
+          <t>349895</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>92197</t>
+          <t>92060</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4456,17 +4496,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MARTIR</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>SEVILLA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4476,7 +4516,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8684643209</t>
+          <t>8135935513</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4487,17 +4527,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08-07-2004</t>
+          <t>07-09-2004</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SAMUELMARTIR5@GMAIL.COM</t>
+          <t>DAAVIIDSIILVAA55@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11-03-2026 06:43:40</t>
+          <t>10-03-2026 17:06:04</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4522,12 +4562,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11-03-2026 06:50:08</t>
+          <t>12-03-2026 16:32:10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4544,10 +4584,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26180523081610007553</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+          <t>26180523126440007753</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4556,24 +4600,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eduardo Alejandro Garcia Dimas</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>350326</t>
+          <t>350032</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>92490</t>
+          <t>92197</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4583,17 +4627,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DANTE AUGUSTO</t>
+          <t xml:space="preserve">SAMUEL </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>MARTIR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>URBINAS</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4603,7 +4647,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8112456466</t>
+          <t>8684643209</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4614,17 +4658,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03-02-2008</t>
+          <t>08-07-2004</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DANTEAMO@HOTMAIL.COM</t>
+          <t>SAMUELMARTIR5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12-03-2026 13:26:54</t>
+          <t>11-03-2026 06:43:40</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4649,12 +4693,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-03-2026 13:28:07</t>
+          <t>11-03-2026 06:50:08</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4671,7 +4715,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26180523122320007723</t>
+          <t>26180523081610007553</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4695,12 +4739,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351067</t>
+          <t>350326</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93231</t>
+          <t>92490</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4710,17 +4754,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ZAIRA MARIBEL</t>
+          <t>DANTE AUGUSTO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>URBINAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4730,31 +4774,35 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8144314757</t>
+          <t>8112456466</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25-03-2003</t>
+          <t>03-02-2008</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ZAIRATORRES000@GMAIL.COM</t>
+          <t>DANTEAMO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-03-2026 10:20:34</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>12-03-2026 13:26:54</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4762,28 +4810,28 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-03-2026 10:21:55</t>
+          <t>12-03-2026 13:28:07</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4794,14 +4842,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26180523214540008065</t>
+          <t>26180523122320007723</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4818,12 +4866,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>351185</t>
+          <t>350348</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93349</t>
+          <t>92512</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4833,17 +4881,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA BELEN </t>
+          <t>JUAN PAULO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>NIÑO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4853,79 +4901,63 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8180247441</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>LOMAS DE SANTA CATARINA 338</t>
-        </is>
-      </c>
+          <t>8123083411</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-03-1983</t>
+          <t>04-01-2011</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MARIABELENLOPEZSOTO1983@GMAIL.COM</t>
+          <t>JPAULO.VALENZ04@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-03-2026 13:35:39</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>12-03-2026 14:39:04</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>16-03-2026 13:39:15</t>
+          <t>12-03-2026 14:42:10</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>16-03-2026 13:38:39</t>
-        </is>
-      </c>
+          <t>11-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4933,14 +4965,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26180523222060008093</t>
+          <t>26180523123810007729</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4957,12 +4989,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>350674</t>
+          <t>349653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>91818</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4972,17 +5004,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA CRISTINA </t>
+          <t>MIRIAM EDITH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GASCA</t>
+          <t xml:space="preserve">CRISTOBAL </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4992,14 +5024,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8130992205</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>SAN AGUSTIN 113</t>
-        </is>
-      </c>
+          <t>8123234107</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5007,64 +5035,56 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23-10-1999</t>
+          <t>21-05-1978</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ANA.GARCIAGSC@GMAIL.COM</t>
+          <t>EDITH@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13-03-2026 19:15:41</t>
+          <t>09-03-2026 19:11:53</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-03-2026 19:20:20</t>
+          <t>09-03-2026 19:13:42</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>13-03-2026 19:19:29</t>
-        </is>
-      </c>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5072,36 +5092,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26180523162710007924</t>
+          <t>26180523026390007333</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>350812</t>
+          <t>351067</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92976</t>
+          <t>93231</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5111,17 +5131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ZAIRA MARIBEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN MARTIN </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5131,28 +5151,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8128718023</t>
+          <t>8144314757</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>29-09-2007</t>
+          <t>25-03-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>MENDEZJULIOCESAR007@GMAIL.COM</t>
+          <t>ZAIRATORRES000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>14-03-2026 13:06:38</t>
+          <t>16-03-2026 10:20:34</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5173,18 +5193,18 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>14-03-2026 13:09:01</t>
+          <t>16-03-2026 10:21:55</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13-06-2026 23:59:59</t>
+          <t>15-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5195,7 +5215,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26180523184000007990</t>
+          <t>26180523214540008065</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5219,12 +5239,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>351478</t>
+          <t>350812</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93642</t>
+          <t>92976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5234,17 +5254,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HERMIONE</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">SAN MARTIN </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CARDOZA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5254,35 +5274,31 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8125978834</t>
+          <t>8128718023</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18-11-2010</t>
+          <t>29-09-2007</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>HERMIONE181110@GMAIL.COM</t>
+          <t>MENDEZJULIOCESAR007@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17-03-2026 12:23:15</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>14-03-2026 13:06:38</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5290,22 +5306,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-03-2026 12:24:21</t>
+          <t>14-03-2026 13:09:01</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>13-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -5322,36 +5338,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26180523251560008181</t>
+          <t>26180523184000007990</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>351935</t>
+          <t>351185</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>94099</t>
+          <t>93349</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5361,17 +5377,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ERIKA</t>
+          <t xml:space="preserve">MARIA BELEN </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5381,10 +5397,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8130742688</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>8180247441</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LOMAS DE SANTA CATARINA 338</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5392,56 +5412,64 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14-03-1982</t>
+          <t>16-03-1983</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ERICKA8214@GMAIL.COM</t>
+          <t>MARIABELENLOPEZSOTO1983@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18-03-2026 18:14:55</t>
+          <t>16-03-2026 13:35:39</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>18-03-2026 18:18:17</t>
+          <t>16-03-2026 13:39:15</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:38:39</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5449,36 +5477,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26180523302540008390</t>
+          <t>26180523222060008093</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Nelson Gabriel Lerma Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>351480</t>
+          <t>351929</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93644</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5488,17 +5516,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PRIA CONSTANZA</t>
+          <t xml:space="preserve">FRESIA </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5508,7 +5536,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8130805757</t>
+          <t>8131387457</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5519,24 +5547,20 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>15-09-2010</t>
+          <t>23-08-2011</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PRIAALVARADO425@GMAIL.COM</t>
+          <t>ESTEBANREYESFRESIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-03-2026 12:26:13</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>18-03-2026 18:11:21</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5544,28 +5568,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>17-03-2026 12:27:54</t>
+          <t>18-03-2026 18:20:15</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>17-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5576,36 +5600,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26180523251640008182</t>
+          <t>26180523302630008391</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Jose Armando  Armijo Campos</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>351068</t>
+          <t>351935</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93232</t>
+          <t>94099</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5615,17 +5639,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KELVIN IVAN</t>
+          <t>ERIKA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RANGEL</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5635,28 +5659,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8136397105</t>
+          <t>8130742688</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10-10-2000</t>
+          <t>14-03-1982</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KELVINRF00@GMAIL.COM</t>
+          <t>ERICKA8214@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-03-2026 10:23:24</t>
+          <t>18-03-2026 18:14:55</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5681,12 +5705,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>16-03-2026 10:24:56</t>
+          <t>18-03-2026 18:18:17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
+          <t>17-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5703,7 +5727,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26180523214650008066</t>
+          <t>26180523302540008390</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5715,24 +5739,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>351209</t>
+          <t>352565</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>94729</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5742,17 +5766,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t>PAOLA MARGARITA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RETTA</t>
+          <t>MATA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HERNADNEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5762,10 +5786,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8117940617</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>8130991600</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SIERRA HIMALAYA 713</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5773,32 +5801,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>07-11-2010</t>
+          <t>30-04-2001</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TAMARARETTAHDZ@GMAIL.COM</t>
+          <t>PAOLA_MAGI134@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-03-2026 14:23:46</t>
+          <t>22-03-2026 09:30:45</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5808,21 +5836,29 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-03-2026 19:03:46</t>
+          <t>22-03-2026 09:39:49</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>21-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>22-03-2026 09:38:12</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5830,7 +5866,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26180523268300008263</t>
+          <t>26180523397010008733</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5854,12 +5890,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>351714</t>
+          <t>352741</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>94905</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5869,17 +5905,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>REGINA YAMILETH</t>
+          <t>GUILLERMO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MOYEDA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5889,63 +5925,79 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8124422040</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>8132564793</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5 DE MAYO 235</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28-11-2002</t>
+          <t>10-02-2006</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>YAMIREGI@HOTMAIL.COM</t>
+          <t>GUILLEMOYEDA17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-03-2026 20:23:05</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>23-03-2026 12:25:08</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-03-2026 20:24:17</t>
+          <t>23-03-2026 12:29:16</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>16-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>23-03-2026 12:28:40</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5953,14 +6005,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26180523273430008281</t>
+          <t>26180523424360008797</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5977,12 +6029,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>351929</t>
+          <t>351478</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>94093</t>
+          <t>93642</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5992,17 +6044,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESIA </t>
+          <t>HERMIONE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>CARDOZA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6012,7 +6064,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8131387457</t>
+          <t>8125978834</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6023,20 +6075,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>23-08-2011</t>
+          <t>18-11-2010</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ESTEBANREYESFRESIA@GMAIL.COM</t>
+          <t>HERMIONE181110@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18-03-2026 18:11:21</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>17-03-2026 12:23:15</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6044,28 +6100,28 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-03-2026 18:20:15</t>
+          <t>17-03-2026 12:24:21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -6076,36 +6132,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26180523302630008391</t>
+          <t>26180523251560008181</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Armando  Armijo Campos</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>351325</t>
+          <t>351480</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>93644</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6115,17 +6171,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIEGO YOTUEL</t>
+          <t>PRIA CONSTANZA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BRIONES</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RIVAS</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6135,47 +6191,43 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8112803747</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>SIERRA PAPAGAYOS 1128</t>
-        </is>
-      </c>
+          <t>8130805757</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>16-01-2002</t>
+          <t>15-09-2010</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DIEGOYOTUEL09@ICLOUD.COM</t>
+          <t>PRIAALVARADO425@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-03-2026 19:03:22</t>
+          <t>17-03-2026 12:26:13</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6185,29 +6237,21 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>18-03-2026 20:53:02</t>
+          <t>17-03-2026 12:27:54</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>18-03-2026 20:51:41</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6215,14 +6259,10 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26180523310530008423</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26180523251640008182</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6231,10 +6271,3019 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
+          <t>Jose Armando  Armijo Campos</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>352534</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>94698</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EDNA CRISTINA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HUITRON</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8129107727</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ELENA PONIATOWSKA 2853</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>28-11-1977</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CRISTINAHUITRON342@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>21-03-2026 12:18:45</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>21-03-2026 12:22:42</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>20-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>21-03-2026 12:22:03</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26180523394190008721</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>351714</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>93878</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>REGINA YAMILETH</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8124422040</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>28-11-2002</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>YAMIREGI@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:23:05</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:24:17</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26180523273430008281</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>352159</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>94323</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BEZLAEL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MERINO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CASTAÑEDA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>8135985714</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>FRANCISCO LANZAGORTA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>20-12-1999</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>BZZCASTANEDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:42:27</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:18:11</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:17:50</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26180523477650009058</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>352953</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>95117</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MARIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>8118474778</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>24-08-1974</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PITASANSOTO08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:35:13</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>25-03-2026 20:52:40</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26180523518760009250</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>353477</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>95641</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EDGAR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>GAYTAN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GAYTAN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>8129714481</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SIERRA DE TARAY 4022</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10-08-1996</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>EDGAR.GGAYTAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>25-03-2026 22:35:43</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>25-03-2026 22:35:44</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>25-03-2026 22:35:44</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26180523519760009253</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>352763</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>94927</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CESAR MAXIMILIANO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>8140057918</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>18-07-2002</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>MAXCST18@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>23-03-2026 14:00:46</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>23-03-2026 14:03:28</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26180523426900008810</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>353159</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>95323</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PATRICIA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELGADILLO </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>8119932442</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TURMALINA 759</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>14-08-2002</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>PGDG15@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>24-03-2026 17:31:59</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>24-03-2026 17:38:30</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>24-03-2026 17:37:52</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26180523475100009045</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>353379</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>95543</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JULIAN DAVID </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8123124656</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>14-09-2002</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>JULIANGZZ226@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:39:38</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:42:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>24-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26180523506340009177</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>354335</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>96499</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARCO </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8116920129</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>13-01-2003</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>MARBAUTISTA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:48:31</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:50:53</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>29-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26180523639400009707</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>353385</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>95549</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FERNANDA CAROLINA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SERNA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AREVALO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8110767372</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>04-09-2006</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>AREVALOCAROO09@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:51:35</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:53:17</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>24-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26180523506750009182</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>351068</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>93232</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>KELVIN IVAN</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RANGEL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FONSECA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>8136397105</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>10-10-2000</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>KELVINRF00@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:23:24</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:24:56</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26180523214650008066</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>351209</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>93373</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TAMARA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RETTA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HERNADNEZ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>8117940617</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>07-11-2010</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>TAMARARETTAHDZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>16-03-2026 14:23:46</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:03:46</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26180523268300008263</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>354301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>96465</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ILAISA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>8118923537</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>19-08-2008</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>ILAISASEVILLA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>30-03-2026 16:58:55</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:00:11</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26180523636020009683</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>354399</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>96563</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>XIMENA GIZELL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LEAL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>VALENCIANO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>8672522452</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>HACIENDA SAN ENRIQUE 118</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>16-04-2005</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>XIMENA_G2005@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:02:30</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:05:53</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:05:22</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26180523645440009734</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>354215</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>96379</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MARITZA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RANGEL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>GUERRA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>8131977797</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>20-11-2010</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>MARITZARG001@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>30-03-2026 13:54:32</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>30-03-2026 13:57:41</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>29-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26180523629060009635</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Nelson Gabriel Lerma Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>354045</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>96209</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MARIA MILAGROS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>8196889686</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>05-01-2002</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>MILAGROS0205@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>29-03-2026 14:31:35</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>29-03-2026 14:33:14</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>28-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26180523607300009561</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Eduardo Alejandro Garcia Dimas</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>351325</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>93489</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DIEGO YOTUEL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BRIONES</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>RIVAS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>8112803747</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SIERRA PAPAGAYOS 1128</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>16-01-2002</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>DIEGOYOTUEL09@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:03:22</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:53:02</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:51:41</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26180523310530008423</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>350674</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>92838</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA CRISTINA </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>GASCA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>8130992205</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SAN AGUSTIN 113</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>23-10-1999</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ANA.GARCIAGSC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:15:41</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:20:20</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:19:29</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26180523162710007924</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>352066</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>94230</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AURELIA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8141860812</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>23-10-2003</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>GONZALEZAURELIA1024@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>19-03-2026 11:43:27</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>30-03-2026 10:35:04</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>29-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26180523623410009602</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>LILIANA SARAHI MORALES VARGAS</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Jose Armando  Armijo Campos</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>352843</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>95007</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHAN ADRIAN </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VANEGAS </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>8117219904</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>03-03-2010</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>JOHAN.DELAPAZ.31@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:12:21</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:13:23</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26180523434500008859</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>352865</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>95029</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LEONARDO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SALVADOR</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>8131145052</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>28-11-2004</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>LEONARDO.28.11.04G@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:39:45</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:41:09</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26180523436370008866</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>352987</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>95151</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SERGIO GAEL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OROZCO </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CADENA</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>8126363916</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA 214</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>22-12-2003</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>GELOROZKO03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>23-03-2026 20:24:53</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>30-03-2026 20:39:46</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>30-03-2026 20:39:02</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26180523650940009760</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>CAROLINA ZUÑIGA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>354435</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>96599</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VICTOR ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>VILLARREAL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>8126327474</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>17-07-2003</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>VICTORAVILLARREALRMZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:45:49</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:48:49</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>29-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26180523648790009750</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
